--- a/docs/WI_ScoreCard_Uso_do_Sistema.xlsx
+++ b/docs/WI_ScoreCard_Uso_do_Sistema.xlsx
@@ -15,9 +15,9 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">'ERROS E SOLUÇÕES'!$3:$3</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'ERROS E SOLUÇÕES'!$A$3:$F$44</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'ERROS E SOLUÇÕES'!$A$3:$F$51</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">JSA!$A$1:$U$34</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">WI!$A$1:$U$73</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">WI!$A$1:$U$87</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">WI!$11:$11</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="584">
   <si>
     <t xml:space="preserve">SITE / CONTA</t>
   </si>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">EQUIPAMENTOS E MATERIAIS NECESSÁRIOS</t>
   </si>
   <si>
-    <t xml:space="preserve">Computador com Windows 10/11, arquivo ScoreCard.exe (V.01.1), VPN da DHL, pasta do SharePoint sincronizada pelo OneDrive e usuário/senha do Summary (BlueYonder). EPI: não se aplica à tarefa (escritório).</t>
+    <t xml:space="preserve">Computador com Windows 10/11, arquivo ScoreCard.exe (V.01.1 ou a mais nova publicada), VPN da DHL, pasta do SharePoint sincronizada pelo OneDrive e usuário/senha do Summary (BlueYonder). EPI: não se aplica à tarefa (escritório).</t>
   </si>
   <si>
     <t xml:space="preserve">SEQUÊNCIA</t>
@@ -197,7 +197,8 @@
 • Confirme que a pasta do SharePoint do Score Card está sincronizada pelo OneDrive.
 • Dê dois cliques no arquivo ScoreCard.exe.
 Na primeira abertura de cada versão o app leva alguns segundos a mais (prepara os arquivos internos). Depois toca a animação de abertura e aparece a tela de login.
-Se o Score Card já estiver aberto, clicar de novo no .exe não abre outra janela: traz para a frente a que já está aberta.</t>
+Se o Score Card já estiver aberto, clicar de novo no .exe não abre outra janela: traz para a frente a que já está aberta.
+Versão nova: quando o responsável publica uma versão mais nova na pasta do SharePoint, aparece uma faixa no topo do app (2ª imagem). Clique em Abrir a pasta, feche o app e use o .exe novo.</t>
     </r>
   </si>
   <si>
@@ -339,7 +340,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> Conferir a versão no rodapé do menu (ex.: V.01.1) e usar sempre o ScoreCard.exe mais recente distribuído pelo responsável pela ferramenta.
+      <t xml:space="preserve"> Conferir a versão no rodapé do menu (ex.: V.01.1). Com a faixa "versão nova", trocar pelo .exe novo antes de extrair: versões antigas apagam o histórico da pasta compartilhada.
 </t>
     </r>
     <r>
@@ -381,12 +382,14 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Na tela de login:
+      <t xml:space="preserve">Na tela de login (a saudação e o fundo mudam com o horário):
 1. Digite o SEU usuário do Summary (BlueYonder).
 2. Digite a SUA senha.
-3. Clique em Entrar (ou tecle Enter).
+3. O olho mostra ou esconde a senha digitada, para conferir antes de entrar.
+4. Clique em Entrar (ou tecle Enter).
+5. Embaixo do card, o ponto da VPN: verde = servidores respondem; amarelo = só parte; vermelho = sem VPN. Clique para conferir de novo.
 Cada pessoa usa a própria credencial. A senha fica só na memória enquanto o app está aberto: não é gravada em arquivo, configuração nem log, e some ao clicar em Sair ou fechar o app.
-Atenção: a senha é conferida no Summary na primeira extração. Se estiver errada, a extração para na etapa "Fazendo login" (ver etapa 6).</t>
+Atenção: a senha é conferida no Summary na primeira extração. Se o Summary recusar a senha 2 vezes seguidas, o app para de tentar (a fila é cancelada) até você clicar em Sair e entrar de novo — isso evita bloquear o usuário.</t>
     </r>
   </si>
   <si>
@@ -488,7 +491,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> Observar o aviso de Caps Lock embaixo da senha. Se a extração falhar no login, conferir a senha no próprio Summary antes de tentar de novo (no máximo 2 tentativas).
+      <t xml:space="preserve"> Observar o aviso de Caps Lock e conferir a senha pelo olho. Se a extração falhar no login, conferir a senha no próprio Summary antes de tentar de novo; depois de 2 recusas o app trava as extrações até um novo login.
 </t>
     </r>
     <r>
@@ -534,6 +537,7 @@
 1. Clique em Escolher pasta.
 2. Selecione a pasta raiz do Score Card (a que contém as pastas das operações) e confirme.
 A escolha fica guardada. Para trocar depois: menu Configurações (Ctrl+9) &gt; Pasta do SharePoint &gt; Alterar pasta (2ª imagem).
+A pasta é a mesma para todo mundo: o que qualquer pessoa extrai ou lança (Headcount e Coverage) aparece para todos que usam o app. O selo "SharePoint · hh:mm" na barra amarela mostra a última leitura da pasta; clicar lê de novo.
 Em Configurações também se escolhe o tema (escuro ou claro), a densidade e o menu recolhido. Isso só muda a aparência, nunca um número.</t>
     </r>
   </si>
@@ -636,7 +640,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> Conferir no ícone do OneDrive (barra de tarefas) que a sincronização está ativa.
+      <t xml:space="preserve"> Conferir no ícone do OneDrive (barra de tarefas) que a sincronização está ativa e, em Configurações &gt; Saúde do sistema, que a pasta aparece em verde (etapa 16).
 </t>
     </r>
     <r>
@@ -1126,7 +1130,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> Clicar em Abrir pasta e conferir se o arquivo está na pasta da operação e do tipo certos. Na pasta fica só o arquivo mais recente de cada operação.
+      <t xml:space="preserve"> Clicar em Abrir pasta e conferir se o arquivo está na pasta da operação e do tipo certos. A extração nova substitui na pasta só o mesmo período; as outras semanas e meses ficam como histórico.
 </t>
     </r>
     <r>
@@ -1529,7 +1533,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> Os dados ficam só neste computador. Não enviar prints com nomes para fora da empresa.
+      <t xml:space="preserve"> Os gestores vão para a pasta do SharePoint da operação (mesmo acesso dos relatórios). Não enviar prints com nomes para fora da empresa.
 </t>
     </r>
     <r>
@@ -1575,7 +1579,8 @@
 2. Para cada gestor digite HC, Dias úteis, Horas/dia e Faltas (em dias inteiros). O que não foi digitado aparece esmaecido e é herdado (HC e horas/dia da semana anterior, dias úteis do calendário, faltas zero).
 3. Confira os cards: HC total, faltas e Presenteísmo (meta 98,00%).
 Presenteísmo = 1 − (Faltas × Horas/dia) ÷ (HC × Dias úteis × Horas/dia).
-"Como o número foi calculado" (abaixo da tabela) mostra a memória de cálculo.</t>
+"Como o número foi calculado" (abaixo da tabela) mostra a memória de cálculo.
+Lançamentos compartilhados (2ª imagem): o que você digita vai para a pasta do SharePoint alguns segundos depois e aparece para as outras pessoas. Quando chega um lançamento de outra pessoa, aparece o aviso "Lançamentos de outra pessoa" (1) e a tela se atualiza — se você estiver digitando, só quando sair do campo. Vale o valor mais recente de cada campo.</t>
     </r>
   </si>
   <si>
@@ -1627,6 +1632,26 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">Q3:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Duas pessoas lançando o mesmo campo ao mesmo tempo.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">HSE1:</t>
     </r>
     <r>
@@ -1678,6 +1703,26 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> Digitar só números; faltas em dias inteiros (0, 1, 2…). O app avisa e não grava valor inválido.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q3:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Combinar quem lança cada operação. Se um valor mudar sozinho, é o lançamento mais novo de outra pessoa: alinhar com ela antes de corrigir.
 </t>
     </r>
     <r>
@@ -1724,7 +1769,10 @@
 2. Confira a tabela: semanas do mês, o mês e o Pico nas colunas; CUBO, EFETIVIDADE, HORA DIRETA, PRESENTEÍSMO, DISPERSÃO e COVERAGE nas linhas, cada um com a meta.
    Verde ✓ = dentro da meta; vermelho ▼ = abaixo; azul ▲ = acima do teto; traço (—) = ainda sem número (não é zero).
 3. O botão Copiar de cada coluna copia os 6 valores na ordem da tela. Cole (Ctrl+V) no Excel ou PowerPoint da apresentação.
-4. Modo apresentação: tela cheia só com a tabela; setas ← → trocam a operação; Esc sai.</t>
+4. Modo apresentação: tela cheia só com a tabela; setas ← → trocam a operação; Esc sai. Automático (2ª imagem, ou barra de espaço) troca a operação sozinho a cada 15 s, 30 s, 1 min ou 2 min, com uma capa entre uma e outra (3ª imagem); a linha amarela mostra o tempo.
+5. No SharePoint: data do relatório mais novo da operação na pasta (de qualquer pessoa).
+6. Selo SharePoint: hora da última leitura da pasta; clique para ler de novo.
+7. A alça no meio da borda do menu (ou Ctrl+B) recolhe o menu e dá mais espaço à tabela.</t>
     </r>
   </si>
   <si>
@@ -1826,7 +1874,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> Traço = falta extração (Week, Month ou Dias de Pico) ou lançamento no Headcount (presenteísmo e cubo). Completar e conferir de novo.
+      <t xml:space="preserve"> Traço = falta extração (Week, Month ou Dias de Pico) ou lançamento no Headcount (presenteísmo e cubo). Antes de extrair, olhar No SharePoint: outra pessoa pode já ter extraído. Completar e conferir de novo.
 </t>
     </r>
     <r>
@@ -1873,7 +1921,7 @@
 2. Na tabela por usuário, ajuste Dias e Horas quando necessário (feriado, afastamento). "Para todos" aplica os mesmos dias/horas a todos os usuários da tela.
 3. Na linha TOTAL, lance a Sinergia cedida e a Sinergia recebida da operação (em horas).
 4. Confira o card Coverage (meta 92,00%).
-Coverage = (Horas LMS − Diretas sem meta) ÷ (Horas Metrics + Sinergia recebida − Sinergia cedida). O que for digitado continua valendo depois de uma nova extração do período.</t>
+Coverage = (Horas LMS − Diretas sem meta) ÷ (Horas Metrics + Sinergia recebida − Sinergia cedida). O que for digitado continua valendo depois de uma nova extração do período e vai para a pasta do SharePoint, valendo para todos (como no Headcount, etapa 10).</t>
     </r>
   </si>
   <si>
@@ -2410,7 +2458,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Em caso de erro: gerar o diagnóstico
+      <t xml:space="preserve">Em caso de erro: saúde do sistema, diagnóstico e backup
 </t>
     </r>
     <r>
@@ -2420,11 +2468,11 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Se algo não funcionar (erro repetido na extração, aviso de erro na tela, número estranho):
-1. Anote a mensagem. Na falha de extração, clique em Ver print do erro.
-2. Menu Configurações (Ctrl+9) &gt; Diagnóstico &gt; Gerar diagnóstico.
-3. O app cria um arquivo .zip na pasta Downloads com o log, a versão e as últimas extrações, sem usuário, senha ou dados de pessoas.
-4. Envie o .zip e a mensagem ao responsável pela ferramenta.</t>
+      <t xml:space="preserve">Se algo não funcionar (erro repetido na extração, aviso de erro na tela, número estranho), menu Configurações (Ctrl+9):
+1. Saúde do sistema (1ª imagem): clique em Conferir agora (1). Cada item (2) tem um ponto verde, amarelo ou vermelho: VPN e servidores, pasta do SharePoint, relatórios na pasta, leitura da pasta, versão do app, versão dos dados, lançamentos compartilhados e backup. Arquivos da pasta que não foram lidos aparecem com o motivo (3); Ler a pasta do zero (4) calcula todos de novo.
+2. Anote a mensagem. Na falha de extração, clique em Ver print do erro.
+3. Diagnóstico (2ª imagem) &gt; Gerar diagnóstico: cria um .zip na pasta Downloads com o log, a versão e as últimas extrações, sem usuário, senha ou dados de pessoas. Envie o .zip e a mensagem ao responsável pela ferramenta.
+4. Backup dos dados (3ª imagem): o app guarda uma cópia por dia (7 dias). Fazer backup agora (1) guarda na hora; Restaurar (2) volta os dados daquele dia, guardando antes o estado atual.</t>
     </r>
   </si>
   <si>
@@ -2476,6 +2524,26 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">Q3:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Restaurar um backup sem necessidade.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">HSE1:</t>
     </r>
     <r>
@@ -2526,7 +2594,27 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> Não editar os arquivos em %APPDATA%\ScoreCard; corrigir a causa e extrair de novo.
+      <t xml:space="preserve"> Não editar os arquivos em %APPDATA%\ScoreCard nem os da pasta Lancamentos; corrigir a causa e extrair de novo.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q3:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Restaurar só com o responsável pela ferramenta. Os lançamentos compartilhados voltam a se juntar com a pasta depois.
 </t>
     </r>
     <r>
@@ -2572,7 +2660,7 @@
 1. Confirme que nenhuma extração está em andamento (rodapé do menu: "Pronto para extrair").
 2. Clique em Sair (apaga usuário e senha da memória).
 3. Feche a janela do Score Card.
-Os lançamentos (Headcount e Coverage) e os indicadores ficam salvos neste computador e aparecem na próxima abertura.</t>
+Os lançamentos (Headcount e Coverage) e os indicadores ficam salvos neste computador e na pasta do SharePoint, e aparecem na próxima abertura (e para as outras pessoas).</t>
     </r>
   </si>
   <si>
@@ -2680,6 +2768,12 @@
     <t xml:space="preserve">Comportamento esperado: o app já está aberto (uma janela só). Procurar na barra de tarefas.</t>
   </si>
   <si>
+    <t xml:space="preserve">Faixa "Há uma versão nova do Score Card…" no topo do app.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clicar em Abrir a pasta, fechar o app e abrir o ScoreCard.exe novo da pasta _ScoreCard.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2</t>
   </si>
   <si>
@@ -2689,9 +2783,21 @@
     <t xml:space="preserve">Digitar usuário e senha do Summary.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ponto da VPN vermelho ("Sem VPN") ou amarelo no login.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conectar a VPN da DHL e clicar no ponto para conferir de novo antes de extrair.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2 e 5</t>
   </si>
   <si>
+    <t xml:space="preserve">"O Summary recusou a senha 2 vezes seguidas…" (extração travada).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clicar em Sair, conferir a senha entrando no próprio Summary e fazer login de novo no app.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extração para em "Fazendo login": "Cliquei em Sign In, mas a tela continua sendo a de login…"</t>
   </si>
   <si>
@@ -2800,6 +2906,30 @@
     <t xml:space="preserve">Tentar de novo; fechar programas que estejam usando a área de transferência; colar com Ctrl+V.</t>
   </si>
   <si>
+    <t xml:space="preserve">10 e 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aviso "Lançamentos de outra pessoa" ou valor que mudou sozinho.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outra pessoa lançou na mesma operação (vale o mais recente). Alinhar com ela antes de corrigir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selo da barra amarela "SharePoint" em vermelho ou "Escolha a pasta".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conferir a pasta em Configurações e a sincronização do OneDrive; ver Saúde do sistema (etapa 16).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relatório em "Arquivos da pasta que não foram lidos" (ex.: Month antigo sem o mês no nome).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extrair aquele tipo/período de novo nesta versão; ele passa a ser lido por todos.</t>
+  </si>
+  <si>
     <t xml:space="preserve">12</t>
   </si>
   <si>
@@ -2863,25 +2993,43 @@
     <t xml:space="preserve">Pela pasta &lt;operação&gt;\&lt;tipo&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">Até a próxima extração do mesmo tipo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O app apaga o arquivo anterior da operação ao salvar o novo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lançamentos e indicadores do app</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computador do usuário (%APPDATA%\ScoreCard)</t>
+    <t xml:space="preserve">Até uma extração nova do mesmo período</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O app apaga só o arquivo do período que a extração nova substitui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lançamentos de Headcount e Coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasta do SharePoint: &lt;operação&gt;\Lancamentos (um arquivo por operação)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acesso conforme permissões do SharePoint; sem credenciais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pelo Score Card (junta e mostra para todos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enquanto a operação usar o Score Card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cópia local e backup do app</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computador do usuário (%APPDATA%\ScoreCard e \backups)</t>
   </si>
   <si>
     <t xml:space="preserve">Perfil do Windows do usuário; sem credenciais gravadas</t>
   </si>
   <si>
-    <t xml:space="preserve">Abrindo o Score Card no mesmo computador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enquanto o app for usado nesse computador</t>
+    <t xml:space="preserve">Configurações &gt; Backup dos dados &gt; Restaurar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backup: últimos 7 dias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O app apaga os backups com mais de 7 dias</t>
   </si>
   <si>
     <t xml:space="preserve">HISTÓRICO DE REVISÃO (inclua linhas conforme necessário)</t>
@@ -2900,6 +3048,12 @@
   </si>
   <si>
     <t xml:space="preserve">Emissão inicial. WI de uso do Score Card versão V.01.1: login, extrações (Extrair Dados e Extrair Múltiplos), Headcount, Início, Coverage, Horas Indiretas, Resultado Gestor, Resultado Turno, diagnóstico, desvios e AST.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasta do SharePoint compartilhada (relatórios e lançamentos de Headcount/Coverage para todos), login com VPN, olho da senha e trava de 2 senhas recusadas, aviso de versão nova, No SharePoint e selo na barra amarela, alça do menu, apresentação automática com capa, Saúde do sistema, backup diário e novos desvios. Prints refeitos.</t>
   </si>
   <si>
     <t xml:space="preserve">APROVAÇÃO (incluir linhas conforme necessário)</t>
@@ -3230,6 +3384,36 @@
     <t xml:space="preserve">Desligar o Caps Lock antes de digitar a senha.</t>
   </si>
   <si>
+    <t xml:space="preserve">Sem VPN  /  VPN: 3 de 6 (ponto vermelho ou amarelo embaixo do card)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VPN desconectada ou parte dos servidores das operações sem resposta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conectar a VPN e clicar no ponto para conferir de novo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extração</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O Summary recusou a senha 2 vezes seguidas. Para não bloquear o seu usuário, o app parou de tentar…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duas extrações seguidas pararam na tela de login do Summary (senha errada ou expirada).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clicar em Sair, conferir a senha no próprio Summary e fazer login de novo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Há uma versão nova do Score Card (V.xx.x) na pasta do SharePoint…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O responsável publicou uma versão mais nova na pasta _ScoreCard.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abrir a pasta, fechar o app e usar o .exe novo.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extração (etapa Fazendo login)</t>
   </si>
   <si>
@@ -3242,9 +3426,6 @@
     <t xml:space="preserve">Clicar em Sair e entrar de novo com a credencial certa. Conferir o acesso direto no Summary. No máximo 2 tentativas, para não bloquear o usuário.</t>
   </si>
   <si>
-    <t xml:space="preserve">Extração</t>
-  </si>
-  <si>
     <t xml:space="preserve">Faça login antes de executar.  /  Credenciais não informadas. Faça login novamente.</t>
   </si>
   <si>
@@ -3626,7 +3807,52 @@
     <t xml:space="preserve">Gerar o diagnóstico e enviar ao responsável pela ferramenta.</t>
   </si>
   <si>
-    <t xml:space="preserve">16</t>
+    <t xml:space="preserve">Lançamentos de outra pessoa — Headcount e Coverage de &lt;operação&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outra pessoa lançou na mesma operação; o valor mais recente de cada campo vale.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nenhuma ação, se esperado. Valor estranho: alinhar com quem lançou.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barra amarela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selo "SharePoint" vermelho  /  "Escolha a pasta do SharePoint"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasta não configurada, sem acesso ou OneDrive parado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configurações &gt; Pasta do SharePoint; conferir o OneDrive e a Saúde do sistema.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 e 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configurações &gt; Saúde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arquivo em "Arquivos da pasta que não foram lidos": arquivo antigo, sem o mês no nome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Month extraído por uma versão anterior (o nome não diz o mês).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extrair aquele mês de novo nesta versão.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configurações &gt; Backup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backup não encontrado.  /  Espere a extração terminar para restaurar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backup apagado (mais de 7 dias) ou extração em andamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escolher outro backup ou esperar a extração terminar.</t>
   </si>
   <si>
     <t xml:space="preserve">SCORE CARD - INFORMAÇÕES GERAIS DA WI</t>
@@ -3902,6 +4128,24 @@
     <t xml:space="preserve">Arquivo .zip gerado em Configurações para o suporte, sem credenciais nem dados de pessoas.</t>
   </si>
   <si>
+    <t xml:space="preserve">Pasta compartilhada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A pasta do SharePoint do Score Card: o que qualquer pessoa extrai ou lança aparece para todos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lançamentos compartilhados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Headcount e Coverage digitados, gravados em &lt;operação&gt;\Lancamentos; vale o valor mais recente de cada campo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saúde do sistema</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quadro em Configurações com VPN, pasta, leitura, versões, lançamentos e backup.</t>
+  </si>
+  <si>
     <t xml:space="preserve">8. ATALHOS DE TECLADO</t>
   </si>
   <si>
@@ -3920,7 +4164,7 @@
     <t xml:space="preserve">Ctrl+B</t>
   </si>
   <si>
-    <t xml:space="preserve">Recolhe ou abre o menu.</t>
+    <t xml:space="preserve">Recolhe ou abre o menu (o mesmo da alça no meio da borda do menu).</t>
   </si>
   <si>
     <t xml:space="preserve">Ctrl+Shift+L</t>
@@ -3945,6 +4189,12 @@
   </si>
   <si>
     <t xml:space="preserve">Trocam a operação no modo apresentação.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Espaço</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liga ou pausa o automático no modo apresentação.</t>
   </si>
   <si>
     <t xml:space="preserve">9. SEGURANÇA DA INFORMAÇÃO</t>
@@ -6421,6 +6671,228 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>66600</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>76320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>1361520</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>3885840</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="44" name="Image 45" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId45"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17588880" y="87344280"/>
+          <a:ext cx="6095520" cy="3809520"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>66600</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>76320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>1361520</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>3885840</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="45" name="Image 46" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId46"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17588880" y="91306800"/>
+          <a:ext cx="6095520" cy="3809520"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>66600</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>76320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>1361520</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>3885840</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="46" name="Image 47" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId47"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17588880" y="95269320"/>
+          <a:ext cx="6095520" cy="3809520"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>66600</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>76320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>1361520</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>3885840</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="47" name="Image 48" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId48"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17588880" y="99231480"/>
+          <a:ext cx="6095520" cy="3809520"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>66600</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>76320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>1361520</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>3885840</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="48" name="Image 49" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId49"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17588880" y="103194000"/>
+          <a:ext cx="6095520" cy="3809520"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>66600</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>76320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>1361520</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>3885840</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="Image 50" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId50"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17588880" y="107156520"/>
+          <a:ext cx="6095520" cy="3809520"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -6441,7 +6913,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="44" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="50" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -6650,7 +7122,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:U73"/>
+  <dimension ref="A1:U87"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.5"/>
@@ -6771,7 +7243,7 @@
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="16"/>
       <c r="E4" s="16"/>
@@ -6801,7 +7273,7 @@
         <v>17</v>
       </c>
       <c r="U4" s="20" t="n">
-        <f aca="false">COUNTIF($P$12:$P$32,$S4)</f>
+        <f aca="false">COUNTIF($P$12:$P$38,$S4)</f>
         <v>11</v>
       </c>
     </row>
@@ -6845,7 +7317,7 @@
         <v>26</v>
       </c>
       <c r="U5" s="20" t="n">
-        <f aca="false">COUNTIF($P$12:$P$32,$S5)</f>
+        <f aca="false">COUNTIF($P$12:$P$38,$S5)</f>
         <v>6</v>
       </c>
     </row>
@@ -6879,7 +7351,7 @@
         <v>29</v>
       </c>
       <c r="U6" s="20" t="n">
-        <f aca="false">COUNTIF($P$12:$P$32,$S6)</f>
+        <f aca="false">COUNTIF($P$12:$P$38,$S6)</f>
         <v>0</v>
       </c>
     </row>
@@ -7046,32 +7518,22 @@
       <c r="U12" s="32"/>
     </row>
     <row r="13" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="30" t="s">
-        <v>49</v>
-      </c>
+      <c r="A13" s="29"/>
+      <c r="B13" s="30"/>
       <c r="C13" s="30"/>
-      <c r="D13" s="31" t="s">
-        <v>50</v>
-      </c>
+      <c r="D13" s="31"/>
       <c r="E13" s="31"/>
       <c r="F13" s="31"/>
       <c r="G13" s="31"/>
       <c r="H13" s="31"/>
       <c r="I13" s="31"/>
-      <c r="J13" s="31" t="s">
-        <v>51</v>
-      </c>
+      <c r="J13" s="31"/>
       <c r="K13" s="31"/>
       <c r="L13" s="31"/>
       <c r="M13" s="31"/>
       <c r="N13" s="31"/>
       <c r="O13" s="31"/>
-      <c r="P13" s="19" t="s">
-        <v>25</v>
-      </c>
+      <c r="P13" s="19"/>
       <c r="Q13" s="32"/>
       <c r="R13" s="32"/>
       <c r="S13" s="32"/>
@@ -7080,14 +7542,14 @@
     </row>
     <row r="14" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C14" s="30"/>
       <c r="D14" s="31" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E14" s="31"/>
       <c r="F14" s="31"/>
@@ -7095,7 +7557,7 @@
       <c r="H14" s="31"/>
       <c r="I14" s="31"/>
       <c r="J14" s="31" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="K14" s="31"/>
       <c r="L14" s="31"/>
@@ -7103,7 +7565,7 @@
       <c r="N14" s="31"/>
       <c r="O14" s="31"/>
       <c r="P14" s="19" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="Q14" s="32"/>
       <c r="R14" s="32"/>
@@ -7112,22 +7574,32 @@
       <c r="U14" s="32"/>
     </row>
     <row r="15" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="29"/>
-      <c r="B15" s="30"/>
+      <c r="A15" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>52</v>
+      </c>
       <c r="C15" s="30"/>
-      <c r="D15" s="31"/>
+      <c r="D15" s="31" t="s">
+        <v>53</v>
+      </c>
       <c r="E15" s="31"/>
       <c r="F15" s="31"/>
       <c r="G15" s="31"/>
       <c r="H15" s="31"/>
       <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
+      <c r="J15" s="31" t="s">
+        <v>54</v>
+      </c>
       <c r="K15" s="31"/>
       <c r="L15" s="31"/>
       <c r="M15" s="31"/>
       <c r="N15" s="31"/>
       <c r="O15" s="31"/>
-      <c r="P15" s="19"/>
+      <c r="P15" s="19" t="s">
+        <v>16</v>
+      </c>
       <c r="Q15" s="32"/>
       <c r="R15" s="32"/>
       <c r="S15" s="32"/>
@@ -7135,32 +7607,22 @@
       <c r="U15" s="32"/>
     </row>
     <row r="16" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="B16" s="30" t="s">
-        <v>55</v>
-      </c>
+      <c r="A16" s="29"/>
+      <c r="B16" s="30"/>
       <c r="C16" s="30"/>
-      <c r="D16" s="31" t="s">
-        <v>56</v>
-      </c>
+      <c r="D16" s="31"/>
       <c r="E16" s="31"/>
       <c r="F16" s="31"/>
       <c r="G16" s="31"/>
       <c r="H16" s="31"/>
       <c r="I16" s="31"/>
-      <c r="J16" s="31" t="s">
-        <v>57</v>
-      </c>
+      <c r="J16" s="31"/>
       <c r="K16" s="31"/>
       <c r="L16" s="31"/>
       <c r="M16" s="31"/>
       <c r="N16" s="31"/>
       <c r="O16" s="31"/>
-      <c r="P16" s="19" t="s">
-        <v>16</v>
-      </c>
+      <c r="P16" s="19"/>
       <c r="Q16" s="32"/>
       <c r="R16" s="32"/>
       <c r="S16" s="32"/>
@@ -7169,14 +7631,14 @@
     </row>
     <row r="17" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C17" s="30"/>
       <c r="D17" s="31" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E17" s="31"/>
       <c r="F17" s="31"/>
@@ -7184,7 +7646,7 @@
       <c r="H17" s="31"/>
       <c r="I17" s="31"/>
       <c r="J17" s="31" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="K17" s="31"/>
       <c r="L17" s="31"/>
@@ -7202,14 +7664,14 @@
     </row>
     <row r="18" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B18" s="30" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C18" s="30"/>
       <c r="D18" s="31" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E18" s="31"/>
       <c r="F18" s="31"/>
@@ -7217,7 +7679,7 @@
       <c r="H18" s="31"/>
       <c r="I18" s="31"/>
       <c r="J18" s="31" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K18" s="31"/>
       <c r="L18" s="31"/>
@@ -7234,22 +7696,32 @@
       <c r="U18" s="32"/>
     </row>
     <row r="19" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="29"/>
-      <c r="B19" s="30"/>
+      <c r="A19" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>61</v>
+      </c>
       <c r="C19" s="30"/>
-      <c r="D19" s="31"/>
+      <c r="D19" s="31" t="s">
+        <v>62</v>
+      </c>
       <c r="E19" s="31"/>
       <c r="F19" s="31"/>
       <c r="G19" s="31"/>
       <c r="H19" s="31"/>
       <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
+      <c r="J19" s="31" t="s">
+        <v>63</v>
+      </c>
       <c r="K19" s="31"/>
       <c r="L19" s="31"/>
       <c r="M19" s="31"/>
       <c r="N19" s="31"/>
       <c r="O19" s="31"/>
-      <c r="P19" s="19"/>
+      <c r="P19" s="19" t="s">
+        <v>16</v>
+      </c>
       <c r="Q19" s="32"/>
       <c r="R19" s="32"/>
       <c r="S19" s="32"/>
@@ -7257,32 +7729,22 @@
       <c r="U19" s="32"/>
     </row>
     <row r="20" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="29" t="n">
-        <v>7</v>
-      </c>
-      <c r="B20" s="30" t="s">
-        <v>64</v>
-      </c>
+      <c r="A20" s="29"/>
+      <c r="B20" s="30"/>
       <c r="C20" s="30"/>
-      <c r="D20" s="31" t="s">
-        <v>65</v>
-      </c>
+      <c r="D20" s="31"/>
       <c r="E20" s="31"/>
       <c r="F20" s="31"/>
       <c r="G20" s="31"/>
       <c r="H20" s="31"/>
       <c r="I20" s="31"/>
-      <c r="J20" s="31" t="s">
-        <v>66</v>
-      </c>
+      <c r="J20" s="31"/>
       <c r="K20" s="31"/>
       <c r="L20" s="31"/>
       <c r="M20" s="31"/>
       <c r="N20" s="31"/>
       <c r="O20" s="31"/>
-      <c r="P20" s="19" t="s">
-        <v>16</v>
-      </c>
+      <c r="P20" s="19"/>
       <c r="Q20" s="32"/>
       <c r="R20" s="32"/>
       <c r="S20" s="32"/>
@@ -7291,14 +7753,14 @@
     </row>
     <row r="21" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B21" s="30" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C21" s="30"/>
       <c r="D21" s="31" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E21" s="31"/>
       <c r="F21" s="31"/>
@@ -7306,7 +7768,7 @@
       <c r="H21" s="31"/>
       <c r="I21" s="31"/>
       <c r="J21" s="31" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K21" s="31"/>
       <c r="L21" s="31"/>
@@ -7323,22 +7785,32 @@
       <c r="U21" s="32"/>
     </row>
     <row r="22" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="29"/>
-      <c r="B22" s="30"/>
+      <c r="A22" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="B22" s="30" t="s">
+        <v>67</v>
+      </c>
       <c r="C22" s="30"/>
-      <c r="D22" s="31"/>
+      <c r="D22" s="31" t="s">
+        <v>68</v>
+      </c>
       <c r="E22" s="31"/>
       <c r="F22" s="31"/>
       <c r="G22" s="31"/>
       <c r="H22" s="31"/>
       <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
+      <c r="J22" s="31" t="s">
+        <v>69</v>
+      </c>
       <c r="K22" s="31"/>
       <c r="L22" s="31"/>
       <c r="M22" s="31"/>
       <c r="N22" s="31"/>
       <c r="O22" s="31"/>
-      <c r="P22" s="19"/>
+      <c r="P22" s="19" t="s">
+        <v>16</v>
+      </c>
       <c r="Q22" s="32"/>
       <c r="R22" s="32"/>
       <c r="S22" s="32"/>
@@ -7346,32 +7818,22 @@
       <c r="U22" s="32"/>
     </row>
     <row r="23" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="29" t="n">
-        <v>9</v>
-      </c>
-      <c r="B23" s="30" t="s">
-        <v>70</v>
-      </c>
+      <c r="A23" s="29"/>
+      <c r="B23" s="30"/>
       <c r="C23" s="30"/>
-      <c r="D23" s="31" t="s">
-        <v>71</v>
-      </c>
+      <c r="D23" s="31"/>
       <c r="E23" s="31"/>
       <c r="F23" s="31"/>
       <c r="G23" s="31"/>
       <c r="H23" s="31"/>
       <c r="I23" s="31"/>
-      <c r="J23" s="31" t="s">
-        <v>72</v>
-      </c>
+      <c r="J23" s="31"/>
       <c r="K23" s="31"/>
       <c r="L23" s="31"/>
       <c r="M23" s="31"/>
       <c r="N23" s="31"/>
       <c r="O23" s="31"/>
-      <c r="P23" s="19" t="s">
-        <v>25</v>
-      </c>
+      <c r="P23" s="19"/>
       <c r="Q23" s="32"/>
       <c r="R23" s="32"/>
       <c r="S23" s="32"/>
@@ -7380,14 +7842,14 @@
     </row>
     <row r="24" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B24" s="30" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C24" s="30"/>
       <c r="D24" s="31" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E24" s="31"/>
       <c r="F24" s="31"/>
@@ -7395,7 +7857,7 @@
       <c r="H24" s="31"/>
       <c r="I24" s="31"/>
       <c r="J24" s="31" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="K24" s="31"/>
       <c r="L24" s="31"/>
@@ -7413,14 +7875,14 @@
     </row>
     <row r="25" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C25" s="30"/>
       <c r="D25" s="31" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E25" s="31"/>
       <c r="F25" s="31"/>
@@ -7428,7 +7890,7 @@
       <c r="H25" s="31"/>
       <c r="I25" s="31"/>
       <c r="J25" s="31" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="K25" s="31"/>
       <c r="L25" s="31"/>
@@ -7445,32 +7907,22 @@
       <c r="U25" s="32"/>
     </row>
     <row r="26" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="29" t="n">
-        <v>12</v>
-      </c>
-      <c r="B26" s="30" t="s">
-        <v>79</v>
-      </c>
+      <c r="A26" s="29"/>
+      <c r="B26" s="30"/>
       <c r="C26" s="30"/>
-      <c r="D26" s="31" t="s">
-        <v>80</v>
-      </c>
+      <c r="D26" s="31"/>
       <c r="E26" s="31"/>
       <c r="F26" s="31"/>
       <c r="G26" s="31"/>
       <c r="H26" s="31"/>
       <c r="I26" s="31"/>
-      <c r="J26" s="31" t="s">
-        <v>81</v>
-      </c>
+      <c r="J26" s="31"/>
       <c r="K26" s="31"/>
       <c r="L26" s="31"/>
       <c r="M26" s="31"/>
       <c r="N26" s="31"/>
       <c r="O26" s="31"/>
-      <c r="P26" s="19" t="s">
-        <v>16</v>
-      </c>
+      <c r="P26" s="19"/>
       <c r="Q26" s="32"/>
       <c r="R26" s="32"/>
       <c r="S26" s="32"/>
@@ -7479,14 +7931,14 @@
     </row>
     <row r="27" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B27" s="30" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C27" s="30"/>
       <c r="D27" s="31" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E27" s="31"/>
       <c r="F27" s="31"/>
@@ -7494,7 +7946,7 @@
       <c r="H27" s="31"/>
       <c r="I27" s="31"/>
       <c r="J27" s="31" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="K27" s="31"/>
       <c r="L27" s="31"/>
@@ -7502,7 +7954,7 @@
       <c r="N27" s="31"/>
       <c r="O27" s="31"/>
       <c r="P27" s="19" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="Q27" s="32"/>
       <c r="R27" s="32"/>
@@ -7511,32 +7963,22 @@
       <c r="U27" s="32"/>
     </row>
     <row r="28" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="29" t="n">
-        <v>14</v>
-      </c>
-      <c r="B28" s="30" t="s">
-        <v>85</v>
-      </c>
+      <c r="A28" s="29"/>
+      <c r="B28" s="30"/>
       <c r="C28" s="30"/>
-      <c r="D28" s="31" t="s">
-        <v>86</v>
-      </c>
+      <c r="D28" s="31"/>
       <c r="E28" s="31"/>
       <c r="F28" s="31"/>
       <c r="G28" s="31"/>
       <c r="H28" s="31"/>
       <c r="I28" s="31"/>
-      <c r="J28" s="31" t="s">
-        <v>87</v>
-      </c>
+      <c r="J28" s="31"/>
       <c r="K28" s="31"/>
       <c r="L28" s="31"/>
       <c r="M28" s="31"/>
       <c r="N28" s="31"/>
       <c r="O28" s="31"/>
-      <c r="P28" s="19" t="s">
-        <v>16</v>
-      </c>
+      <c r="P28" s="19"/>
       <c r="Q28" s="32"/>
       <c r="R28" s="32"/>
       <c r="S28" s="32"/>
@@ -7568,14 +8010,14 @@
     </row>
     <row r="30" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="29" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B30" s="30" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C30" s="30"/>
       <c r="D30" s="31" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E30" s="31"/>
       <c r="F30" s="31"/>
@@ -7583,7 +8025,7 @@
       <c r="H30" s="31"/>
       <c r="I30" s="31"/>
       <c r="J30" s="31" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K30" s="31"/>
       <c r="L30" s="31"/>
@@ -7601,14 +8043,14 @@
     </row>
     <row r="31" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="29" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C31" s="30"/>
       <c r="D31" s="31" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="E31" s="31"/>
       <c r="F31" s="31"/>
@@ -7616,7 +8058,7 @@
       <c r="H31" s="31"/>
       <c r="I31" s="31"/>
       <c r="J31" s="31" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="K31" s="31"/>
       <c r="L31" s="31"/>
@@ -7633,248 +8075,242 @@
       <c r="U31" s="32"/>
     </row>
     <row r="32" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="33" t="n">
+      <c r="A32" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="B32" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" s="30"/>
+      <c r="D32" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q32" s="32"/>
+      <c r="R32" s="32"/>
+      <c r="S32" s="32"/>
+      <c r="T32" s="32"/>
+      <c r="U32" s="32"/>
+    </row>
+    <row r="33" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="29"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="19"/>
+      <c r="Q33" s="32"/>
+      <c r="R33" s="32"/>
+      <c r="S33" s="32"/>
+      <c r="T33" s="32"/>
+      <c r="U33" s="32"/>
+    </row>
+    <row r="34" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="29" t="n">
+        <v>15</v>
+      </c>
+      <c r="B34" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="30"/>
+      <c r="D34" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="31"/>
+      <c r="I34" s="31"/>
+      <c r="J34" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="K34" s="31"/>
+      <c r="L34" s="31"/>
+      <c r="M34" s="31"/>
+      <c r="N34" s="31"/>
+      <c r="O34" s="31"/>
+      <c r="P34" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q34" s="32"/>
+      <c r="R34" s="32"/>
+      <c r="S34" s="32"/>
+      <c r="T34" s="32"/>
+      <c r="U34" s="32"/>
+    </row>
+    <row r="35" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="B35" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="C35" s="30"/>
+      <c r="D35" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="31"/>
+      <c r="J35" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="K35" s="31"/>
+      <c r="L35" s="31"/>
+      <c r="M35" s="31"/>
+      <c r="N35" s="31"/>
+      <c r="O35" s="31"/>
+      <c r="P35" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q35" s="32"/>
+      <c r="R35" s="32"/>
+      <c r="S35" s="32"/>
+      <c r="T35" s="32"/>
+      <c r="U35" s="32"/>
+    </row>
+    <row r="36" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="29"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="31"/>
+      <c r="I36" s="31"/>
+      <c r="J36" s="31"/>
+      <c r="K36" s="31"/>
+      <c r="L36" s="31"/>
+      <c r="M36" s="31"/>
+      <c r="N36" s="31"/>
+      <c r="O36" s="31"/>
+      <c r="P36" s="19"/>
+      <c r="Q36" s="32"/>
+      <c r="R36" s="32"/>
+      <c r="S36" s="32"/>
+      <c r="T36" s="32"/>
+      <c r="U36" s="32"/>
+    </row>
+    <row r="37" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="29"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+      <c r="K37" s="31"/>
+      <c r="L37" s="31"/>
+      <c r="M37" s="31"/>
+      <c r="N37" s="31"/>
+      <c r="O37" s="31"/>
+      <c r="P37" s="19"/>
+      <c r="Q37" s="32"/>
+      <c r="R37" s="32"/>
+      <c r="S37" s="32"/>
+      <c r="T37" s="32"/>
+      <c r="U37" s="32"/>
+    </row>
+    <row r="38" customFormat="false" ht="312" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="33" t="n">
         <v>17</v>
       </c>
-      <c r="B32" s="34" t="s">
+      <c r="B38" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="C32" s="34"/>
-      <c r="D32" s="35" t="s">
+      <c r="C38" s="34"/>
+      <c r="D38" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="35"/>
-      <c r="J32" s="35" t="s">
+      <c r="E38" s="35"/>
+      <c r="F38" s="35"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="35"/>
+      <c r="I38" s="35"/>
+      <c r="J38" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="K32" s="35"/>
-      <c r="L32" s="35"/>
-      <c r="M32" s="35"/>
-      <c r="N32" s="35"/>
-      <c r="O32" s="35"/>
-      <c r="P32" s="36" t="s">
+      <c r="K38" s="35"/>
+      <c r="L38" s="35"/>
+      <c r="M38" s="35"/>
+      <c r="N38" s="35"/>
+      <c r="O38" s="35"/>
+      <c r="P38" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="Q32" s="37"/>
-      <c r="R32" s="37"/>
-      <c r="S32" s="37"/>
-      <c r="T32" s="37"/>
-      <c r="U32" s="37"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="26" t="s">
+      <c r="Q38" s="37"/>
+      <c r="R38" s="37"/>
+      <c r="S38" s="37"/>
+      <c r="T38" s="37"/>
+      <c r="U38" s="37"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="27" t="s">
+      <c r="B40" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="C34" s="27"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="27"/>
-      <c r="I34" s="28" t="s">
+      <c r="C40" s="27"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27"/>
+      <c r="I40" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="J34" s="28"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="28"/>
-      <c r="M34" s="28"/>
-      <c r="N34" s="28"/>
-      <c r="O34" s="28"/>
-      <c r="P34" s="28"/>
-      <c r="Q34" s="28"/>
-      <c r="R34" s="28"/>
-      <c r="S34" s="28"/>
-      <c r="T34" s="28"/>
-      <c r="U34" s="28"/>
-    </row>
-    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="B35" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="J35" s="16"/>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="16"/>
-      <c r="O35" s="16"/>
-      <c r="P35" s="16"/>
-      <c r="Q35" s="16"/>
-      <c r="R35" s="16"/>
-      <c r="S35" s="16"/>
-      <c r="T35" s="16"/>
-      <c r="U35" s="16"/>
-    </row>
-    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="B36" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22"/>
-      <c r="I36" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="J36" s="16"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="16"/>
-      <c r="O36" s="16"/>
-      <c r="P36" s="16"/>
-      <c r="Q36" s="16"/>
-      <c r="R36" s="16"/>
-      <c r="S36" s="16"/>
-      <c r="T36" s="16"/>
-      <c r="U36" s="16"/>
-    </row>
-    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="B37" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="22"/>
-      <c r="H37" s="22"/>
-      <c r="I37" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="J37" s="16"/>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="16"/>
-      <c r="O37" s="16"/>
-      <c r="P37" s="16"/>
-      <c r="Q37" s="16"/>
-      <c r="R37" s="16"/>
-      <c r="S37" s="16"/>
-      <c r="T37" s="16"/>
-      <c r="U37" s="16"/>
-    </row>
-    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="38" t="s">
-        <v>107</v>
-      </c>
-      <c r="B38" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="22"/>
-      <c r="I38" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="J38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="16"/>
-      <c r="O38" s="16"/>
-      <c r="P38" s="16"/>
-      <c r="Q38" s="16"/>
-      <c r="R38" s="16"/>
-      <c r="S38" s="16"/>
-      <c r="T38" s="16"/>
-      <c r="U38" s="16"/>
-    </row>
-    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="B39" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="22"/>
-      <c r="H39" s="22"/>
-      <c r="I39" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="J39" s="16"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="16"/>
-      <c r="O39" s="16"/>
-      <c r="P39" s="16"/>
-      <c r="Q39" s="16"/>
-      <c r="R39" s="16"/>
-      <c r="S39" s="16"/>
-      <c r="T39" s="16"/>
-      <c r="U39" s="16"/>
-    </row>
-    <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="B40" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="C40" s="22"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="22"/>
-      <c r="H40" s="22"/>
-      <c r="I40" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="J40" s="16"/>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="16"/>
-      <c r="O40" s="16"/>
-      <c r="P40" s="16"/>
-      <c r="Q40" s="16"/>
-      <c r="R40" s="16"/>
-      <c r="S40" s="16"/>
-      <c r="T40" s="16"/>
-      <c r="U40" s="16"/>
+      <c r="J40" s="28"/>
+      <c r="K40" s="28"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="28"/>
+      <c r="N40" s="28"/>
+      <c r="O40" s="28"/>
+      <c r="P40" s="28"/>
+      <c r="Q40" s="28"/>
+      <c r="R40" s="28"/>
+      <c r="S40" s="28"/>
+      <c r="T40" s="28"/>
+      <c r="U40" s="28"/>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="38" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="C41" s="22"/>
       <c r="D41" s="22"/>
@@ -7883,7 +8319,7 @@
       <c r="G41" s="22"/>
       <c r="H41" s="22"/>
       <c r="I41" s="16" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="J41" s="16"/>
       <c r="K41" s="16"/>
@@ -7900,10 +8336,10 @@
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="38" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="B42" s="22" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="C42" s="22"/>
       <c r="D42" s="22"/>
@@ -7912,7 +8348,7 @@
       <c r="G42" s="22"/>
       <c r="H42" s="22"/>
       <c r="I42" s="16" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="J42" s="16"/>
       <c r="K42" s="16"/>
@@ -7929,10 +8365,10 @@
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="38" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="B43" s="22" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="C43" s="22"/>
       <c r="D43" s="22"/>
@@ -7941,7 +8377,7 @@
       <c r="G43" s="22"/>
       <c r="H43" s="22"/>
       <c r="I43" s="16" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="J43" s="16"/>
       <c r="K43" s="16"/>
@@ -7958,10 +8394,10 @@
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="38" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B44" s="22" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="C44" s="22"/>
       <c r="D44" s="22"/>
@@ -7970,7 +8406,7 @@
       <c r="G44" s="22"/>
       <c r="H44" s="22"/>
       <c r="I44" s="16" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="J44" s="16"/>
       <c r="K44" s="16"/>
@@ -7987,10 +8423,10 @@
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="38" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="B45" s="22" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="C45" s="22"/>
       <c r="D45" s="22"/>
@@ -7999,7 +8435,7 @@
       <c r="G45" s="22"/>
       <c r="H45" s="22"/>
       <c r="I45" s="16" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="J45" s="16"/>
       <c r="K45" s="16"/>
@@ -8016,10 +8452,10 @@
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="38" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="B46" s="22" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="C46" s="22"/>
       <c r="D46" s="22"/>
@@ -8028,7 +8464,7 @@
       <c r="G46" s="22"/>
       <c r="H46" s="22"/>
       <c r="I46" s="16" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="J46" s="16"/>
       <c r="K46" s="16"/>
@@ -8045,10 +8481,10 @@
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="38" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="B47" s="22" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="C47" s="22"/>
       <c r="D47" s="22"/>
@@ -8057,7 +8493,7 @@
       <c r="G47" s="22"/>
       <c r="H47" s="22"/>
       <c r="I47" s="16" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="J47" s="16"/>
       <c r="K47" s="16"/>
@@ -8074,10 +8510,10 @@
     </row>
     <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="38" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="B48" s="22" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="C48" s="22"/>
       <c r="D48" s="22"/>
@@ -8086,7 +8522,7 @@
       <c r="G48" s="22"/>
       <c r="H48" s="22"/>
       <c r="I48" s="16" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="J48" s="16"/>
       <c r="K48" s="16"/>
@@ -8103,10 +8539,10 @@
     </row>
     <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="38" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="C49" s="22"/>
       <c r="D49" s="22"/>
@@ -8115,7 +8551,7 @@
       <c r="G49" s="22"/>
       <c r="H49" s="22"/>
       <c r="I49" s="16" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="J49" s="16"/>
       <c r="K49" s="16"/>
@@ -8130,12 +8566,12 @@
       <c r="T49" s="16"/>
       <c r="U49" s="16"/>
     </row>
-    <row r="50" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="38" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="C50" s="22"/>
       <c r="D50" s="22"/>
@@ -8144,7 +8580,7 @@
       <c r="G50" s="22"/>
       <c r="H50" s="22"/>
       <c r="I50" s="16" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="J50" s="16"/>
       <c r="K50" s="16"/>
@@ -8161,10 +8597,10 @@
     </row>
     <row r="51" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="38" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="B51" s="22" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="C51" s="22"/>
       <c r="D51" s="22"/>
@@ -8173,7 +8609,7 @@
       <c r="G51" s="22"/>
       <c r="H51" s="22"/>
       <c r="I51" s="16" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="J51" s="16"/>
       <c r="K51" s="16"/>
@@ -8189,523 +8625,935 @@
       <c r="U51" s="16"/>
     </row>
     <row r="52" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="39" t="s">
+      <c r="A52" s="38" t="s">
+        <v>125</v>
+      </c>
+      <c r="B52" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="C52" s="22"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="22"/>
+      <c r="H52" s="22"/>
+      <c r="I52" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="J52" s="16"/>
+      <c r="K52" s="16"/>
+      <c r="L52" s="16"/>
+      <c r="M52" s="16"/>
+      <c r="N52" s="16"/>
+      <c r="O52" s="16"/>
+      <c r="P52" s="16"/>
+      <c r="Q52" s="16"/>
+      <c r="R52" s="16"/>
+      <c r="S52" s="16"/>
+      <c r="T52" s="16"/>
+      <c r="U52" s="16"/>
+    </row>
+    <row r="53" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="38" t="s">
+        <v>130</v>
+      </c>
+      <c r="B53" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="C53" s="22"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="22"/>
+      <c r="H53" s="22"/>
+      <c r="I53" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="J53" s="16"/>
+      <c r="K53" s="16"/>
+      <c r="L53" s="16"/>
+      <c r="M53" s="16"/>
+      <c r="N53" s="16"/>
+      <c r="O53" s="16"/>
+      <c r="P53" s="16"/>
+      <c r="Q53" s="16"/>
+      <c r="R53" s="16"/>
+      <c r="S53" s="16"/>
+      <c r="T53" s="16"/>
+      <c r="U53" s="16"/>
+    </row>
+    <row r="54" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="38" t="s">
+        <v>133</v>
+      </c>
+      <c r="B54" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="C54" s="22"/>
+      <c r="D54" s="22"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="22"/>
+      <c r="G54" s="22"/>
+      <c r="H54" s="22"/>
+      <c r="I54" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="J54" s="16"/>
+      <c r="K54" s="16"/>
+      <c r="L54" s="16"/>
+      <c r="M54" s="16"/>
+      <c r="N54" s="16"/>
+      <c r="O54" s="16"/>
+      <c r="P54" s="16"/>
+      <c r="Q54" s="16"/>
+      <c r="R54" s="16"/>
+      <c r="S54" s="16"/>
+      <c r="T54" s="16"/>
+      <c r="U54" s="16"/>
+    </row>
+    <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="B55" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="C55" s="22"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="22"/>
+      <c r="H55" s="22"/>
+      <c r="I55" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="J55" s="16"/>
+      <c r="K55" s="16"/>
+      <c r="L55" s="16"/>
+      <c r="M55" s="16"/>
+      <c r="N55" s="16"/>
+      <c r="O55" s="16"/>
+      <c r="P55" s="16"/>
+      <c r="Q55" s="16"/>
+      <c r="R55" s="16"/>
+      <c r="S55" s="16"/>
+      <c r="T55" s="16"/>
+      <c r="U55" s="16"/>
+    </row>
+    <row r="56" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="38" t="s">
+        <v>139</v>
+      </c>
+      <c r="B56" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="C56" s="22"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="22"/>
+      <c r="G56" s="22"/>
+      <c r="H56" s="22"/>
+      <c r="I56" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="J56" s="16"/>
+      <c r="K56" s="16"/>
+      <c r="L56" s="16"/>
+      <c r="M56" s="16"/>
+      <c r="N56" s="16"/>
+      <c r="O56" s="16"/>
+      <c r="P56" s="16"/>
+      <c r="Q56" s="16"/>
+      <c r="R56" s="16"/>
+      <c r="S56" s="16"/>
+      <c r="T56" s="16"/>
+      <c r="U56" s="16"/>
+    </row>
+    <row r="57" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="B57" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="C57" s="22"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="22"/>
+      <c r="H57" s="22"/>
+      <c r="I57" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="J57" s="16"/>
+      <c r="K57" s="16"/>
+      <c r="L57" s="16"/>
+      <c r="M57" s="16"/>
+      <c r="N57" s="16"/>
+      <c r="O57" s="16"/>
+      <c r="P57" s="16"/>
+      <c r="Q57" s="16"/>
+      <c r="R57" s="16"/>
+      <c r="S57" s="16"/>
+      <c r="T57" s="16"/>
+      <c r="U57" s="16"/>
+    </row>
+    <row r="58" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="B58" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="C58" s="22"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="22"/>
+      <c r="I58" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="J58" s="16"/>
+      <c r="K58" s="16"/>
+      <c r="L58" s="16"/>
+      <c r="M58" s="16"/>
+      <c r="N58" s="16"/>
+      <c r="O58" s="16"/>
+      <c r="P58" s="16"/>
+      <c r="Q58" s="16"/>
+      <c r="R58" s="16"/>
+      <c r="S58" s="16"/>
+      <c r="T58" s="16"/>
+      <c r="U58" s="16"/>
+    </row>
+    <row r="59" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="38" t="s">
         <v>147</v>
       </c>
-      <c r="B52" s="40" t="s">
+      <c r="B59" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="C52" s="40"/>
-      <c r="D52" s="40"/>
-      <c r="E52" s="40"/>
-      <c r="F52" s="40"/>
-      <c r="G52" s="40"/>
-      <c r="H52" s="40"/>
-      <c r="I52" s="24" t="s">
+      <c r="C59" s="22"/>
+      <c r="D59" s="22"/>
+      <c r="E59" s="22"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="22"/>
+      <c r="H59" s="22"/>
+      <c r="I59" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J52" s="24"/>
-      <c r="K52" s="24"/>
-      <c r="L52" s="24"/>
-      <c r="M52" s="24"/>
-      <c r="N52" s="24"/>
-      <c r="O52" s="24"/>
-      <c r="P52" s="24"/>
-      <c r="Q52" s="24"/>
-      <c r="R52" s="24"/>
-      <c r="S52" s="24"/>
-      <c r="T52" s="24"/>
-      <c r="U52" s="24"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="41" t="s">
+      <c r="J59" s="16"/>
+      <c r="K59" s="16"/>
+      <c r="L59" s="16"/>
+      <c r="M59" s="16"/>
+      <c r="N59" s="16"/>
+      <c r="O59" s="16"/>
+      <c r="P59" s="16"/>
+      <c r="Q59" s="16"/>
+      <c r="R59" s="16"/>
+      <c r="S59" s="16"/>
+      <c r="T59" s="16"/>
+      <c r="U59" s="16"/>
+    </row>
+    <row r="60" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="38" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="55" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="42" t="s">
+      <c r="B60" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="B55" s="42"/>
-      <c r="C55" s="42"/>
-      <c r="D55" s="42"/>
-      <c r="E55" s="42"/>
-      <c r="F55" s="42"/>
-      <c r="G55" s="42"/>
-      <c r="H55" s="42"/>
-      <c r="I55" s="42"/>
-      <c r="J55" s="42"/>
-      <c r="K55" s="42"/>
-      <c r="L55" s="42"/>
-      <c r="M55" s="42"/>
-      <c r="N55" s="42"/>
-      <c r="O55" s="42"/>
-      <c r="P55" s="42"/>
-      <c r="Q55" s="42"/>
-      <c r="R55" s="42"/>
-      <c r="S55" s="42"/>
-      <c r="T55" s="42"/>
-      <c r="U55" s="42"/>
-    </row>
-    <row r="56" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="15" t="s">
+      <c r="C60" s="22"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="22"/>
+      <c r="F60" s="22"/>
+      <c r="G60" s="22"/>
+      <c r="H60" s="22"/>
+      <c r="I60" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="B56" s="15"/>
-      <c r="C56" s="15" t="s">
+      <c r="J60" s="16"/>
+      <c r="K60" s="16"/>
+      <c r="L60" s="16"/>
+      <c r="M60" s="16"/>
+      <c r="N60" s="16"/>
+      <c r="O60" s="16"/>
+      <c r="P60" s="16"/>
+      <c r="Q60" s="16"/>
+      <c r="R60" s="16"/>
+      <c r="S60" s="16"/>
+      <c r="T60" s="16"/>
+      <c r="U60" s="16"/>
+    </row>
+    <row r="61" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="B61" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="D56" s="15"/>
-      <c r="E56" s="15" t="s">
+      <c r="C61" s="22"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="22"/>
+      <c r="H61" s="22"/>
+      <c r="I61" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="F56" s="15"/>
-      <c r="G56" s="15"/>
-      <c r="H56" s="15"/>
-      <c r="I56" s="15" t="s">
+      <c r="J61" s="16"/>
+      <c r="K61" s="16"/>
+      <c r="L61" s="16"/>
+      <c r="M61" s="16"/>
+      <c r="N61" s="16"/>
+      <c r="O61" s="16"/>
+      <c r="P61" s="16"/>
+      <c r="Q61" s="16"/>
+      <c r="R61" s="16"/>
+      <c r="S61" s="16"/>
+      <c r="T61" s="16"/>
+      <c r="U61" s="16"/>
+    </row>
+    <row r="62" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="38" t="s">
         <v>155</v>
       </c>
-      <c r="J56" s="15"/>
-      <c r="K56" s="15"/>
-      <c r="L56" s="15"/>
-      <c r="M56" s="15" t="s">
+      <c r="B62" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="N56" s="15"/>
-      <c r="O56" s="15"/>
-      <c r="P56" s="15"/>
-      <c r="Q56" s="15"/>
-      <c r="R56" s="15" t="s">
+      <c r="C62" s="22"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="22"/>
+      <c r="H62" s="22"/>
+      <c r="I62" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="S56" s="15"/>
-      <c r="T56" s="15"/>
-      <c r="U56" s="15"/>
-    </row>
-    <row r="57" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="43" t="s">
+      <c r="J62" s="16"/>
+      <c r="K62" s="16"/>
+      <c r="L62" s="16"/>
+      <c r="M62" s="16"/>
+      <c r="N62" s="16"/>
+      <c r="O62" s="16"/>
+      <c r="P62" s="16"/>
+      <c r="Q62" s="16"/>
+      <c r="R62" s="16"/>
+      <c r="S62" s="16"/>
+      <c r="T62" s="16"/>
+      <c r="U62" s="16"/>
+    </row>
+    <row r="63" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="B57" s="43"/>
-      <c r="C57" s="43" t="s">
+      <c r="B63" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="D57" s="43"/>
-      <c r="E57" s="43" t="s">
-        <v>160</v>
-      </c>
-      <c r="F57" s="43"/>
-      <c r="G57" s="43"/>
-      <c r="H57" s="43"/>
-      <c r="I57" s="43" t="s">
-        <v>160</v>
-      </c>
-      <c r="J57" s="43"/>
-      <c r="K57" s="43"/>
-      <c r="L57" s="43"/>
-      <c r="M57" s="43" t="s">
-        <v>160</v>
-      </c>
-      <c r="N57" s="43"/>
-      <c r="O57" s="43"/>
-      <c r="P57" s="43"/>
-      <c r="Q57" s="43"/>
-      <c r="R57" s="43" t="s">
-        <v>160</v>
-      </c>
-      <c r="S57" s="43"/>
-      <c r="T57" s="43"/>
-      <c r="U57" s="43"/>
-    </row>
-    <row r="58" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="43" t="s">
-        <v>161</v>
-      </c>
-      <c r="B58" s="43"/>
-      <c r="C58" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="D58" s="43"/>
-      <c r="E58" s="43" t="s">
-        <v>163</v>
-      </c>
-      <c r="F58" s="43"/>
-      <c r="G58" s="43"/>
-      <c r="H58" s="43"/>
-      <c r="I58" s="43" t="s">
-        <v>164</v>
-      </c>
-      <c r="J58" s="43"/>
-      <c r="K58" s="43"/>
-      <c r="L58" s="43"/>
-      <c r="M58" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="N58" s="43"/>
-      <c r="O58" s="43"/>
-      <c r="P58" s="43"/>
-      <c r="Q58" s="43"/>
-      <c r="R58" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="S58" s="43"/>
-      <c r="T58" s="43"/>
-      <c r="U58" s="43"/>
-    </row>
-    <row r="59" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="B59" s="43"/>
-      <c r="C59" s="43" t="s">
-        <v>168</v>
-      </c>
-      <c r="D59" s="43"/>
-      <c r="E59" s="43" t="s">
-        <v>169</v>
-      </c>
-      <c r="F59" s="43"/>
-      <c r="G59" s="43"/>
-      <c r="H59" s="43"/>
-      <c r="I59" s="43" t="s">
-        <v>170</v>
-      </c>
-      <c r="J59" s="43"/>
-      <c r="K59" s="43"/>
-      <c r="L59" s="43"/>
-      <c r="M59" s="43" t="s">
-        <v>171</v>
-      </c>
-      <c r="N59" s="43"/>
-      <c r="O59" s="43"/>
-      <c r="P59" s="43"/>
-      <c r="Q59" s="43"/>
-      <c r="R59" s="43" t="s">
-        <v>160</v>
-      </c>
-      <c r="S59" s="43"/>
-      <c r="T59" s="43"/>
-      <c r="U59" s="43"/>
-    </row>
-    <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="61" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="B61" s="15"/>
-      <c r="C61" s="15"/>
-      <c r="D61" s="15"/>
-      <c r="E61" s="15"/>
-      <c r="F61" s="15"/>
-      <c r="G61" s="15"/>
-      <c r="H61" s="15"/>
-      <c r="I61" s="15"/>
-      <c r="J61" s="15"/>
-      <c r="K61" s="15"/>
-      <c r="L61" s="15"/>
-      <c r="M61" s="15"/>
-      <c r="N61" s="15"/>
-      <c r="O61" s="15"/>
-      <c r="P61" s="15"/>
-      <c r="Q61" s="15"/>
-      <c r="R61" s="15"/>
-      <c r="S61" s="15"/>
-      <c r="T61" s="15"/>
-      <c r="U61" s="15"/>
-    </row>
-    <row r="62" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="B62" s="15"/>
-      <c r="C62" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="D62" s="15"/>
-      <c r="E62" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="F62" s="15"/>
-      <c r="G62" s="15"/>
-      <c r="H62" s="15"/>
-      <c r="I62" s="15"/>
-      <c r="J62" s="15"/>
-      <c r="K62" s="15"/>
-      <c r="L62" s="15"/>
-      <c r="M62" s="15"/>
-      <c r="N62" s="15"/>
-      <c r="O62" s="15"/>
-      <c r="P62" s="15"/>
-      <c r="Q62" s="15"/>
-      <c r="R62" s="15"/>
-      <c r="S62" s="15"/>
-      <c r="T62" s="15"/>
-      <c r="U62" s="15"/>
-    </row>
-    <row r="63" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="B63" s="20"/>
-      <c r="C63" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="D63" s="20"/>
-      <c r="E63" s="22" t="s">
-        <v>177</v>
-      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
       <c r="F63" s="22"/>
       <c r="G63" s="22"/>
       <c r="H63" s="22"/>
-      <c r="I63" s="22"/>
-      <c r="J63" s="22"/>
-      <c r="K63" s="22"/>
-      <c r="L63" s="22"/>
-      <c r="M63" s="22"/>
-      <c r="N63" s="22"/>
-      <c r="O63" s="22"/>
-      <c r="P63" s="22"/>
-      <c r="Q63" s="22"/>
-      <c r="R63" s="22"/>
-      <c r="S63" s="22"/>
-      <c r="T63" s="22"/>
-      <c r="U63" s="22"/>
-    </row>
-    <row r="64" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="22"/>
-      <c r="B64" s="22"/>
-      <c r="C64" s="22"/>
-      <c r="D64" s="22"/>
-      <c r="E64" s="22"/>
-      <c r="F64" s="22"/>
-      <c r="G64" s="22"/>
-      <c r="H64" s="22"/>
-      <c r="I64" s="22"/>
-      <c r="J64" s="22"/>
-      <c r="K64" s="22"/>
-      <c r="L64" s="22"/>
-      <c r="M64" s="22"/>
-      <c r="N64" s="22"/>
-      <c r="O64" s="22"/>
-      <c r="P64" s="22"/>
-      <c r="Q64" s="22"/>
-      <c r="R64" s="22"/>
-      <c r="S64" s="22"/>
-      <c r="T64" s="22"/>
-      <c r="U64" s="22"/>
-    </row>
-    <row r="65" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="22"/>
-      <c r="B65" s="22"/>
-      <c r="C65" s="22"/>
-      <c r="D65" s="22"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22"/>
-      <c r="G65" s="22"/>
-      <c r="H65" s="22"/>
-      <c r="I65" s="22"/>
-      <c r="J65" s="22"/>
-      <c r="K65" s="22"/>
-      <c r="L65" s="22"/>
-      <c r="M65" s="22"/>
-      <c r="N65" s="22"/>
-      <c r="O65" s="22"/>
-      <c r="P65" s="22"/>
-      <c r="Q65" s="22"/>
-      <c r="R65" s="22"/>
-      <c r="S65" s="22"/>
-      <c r="T65" s="22"/>
-      <c r="U65" s="22"/>
+      <c r="I63" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="J63" s="16"/>
+      <c r="K63" s="16"/>
+      <c r="L63" s="16"/>
+      <c r="M63" s="16"/>
+      <c r="N63" s="16"/>
+      <c r="O63" s="16"/>
+      <c r="P63" s="16"/>
+      <c r="Q63" s="16"/>
+      <c r="R63" s="16"/>
+      <c r="S63" s="16"/>
+      <c r="T63" s="16"/>
+      <c r="U63" s="16"/>
+    </row>
+    <row r="64" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="39" t="s">
+        <v>161</v>
+      </c>
+      <c r="B64" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="C64" s="40"/>
+      <c r="D64" s="40"/>
+      <c r="E64" s="40"/>
+      <c r="F64" s="40"/>
+      <c r="G64" s="40"/>
+      <c r="H64" s="40"/>
+      <c r="I64" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="J64" s="24"/>
+      <c r="K64" s="24"/>
+      <c r="L64" s="24"/>
+      <c r="M64" s="24"/>
+      <c r="N64" s="24"/>
+      <c r="O64" s="24"/>
+      <c r="P64" s="24"/>
+      <c r="Q64" s="24"/>
+      <c r="R64" s="24"/>
+      <c r="S64" s="24"/>
+      <c r="T64" s="24"/>
+      <c r="U64" s="24"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="41" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="67" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="B67" s="15"/>
-      <c r="C67" s="15"/>
-      <c r="D67" s="15"/>
-      <c r="E67" s="15"/>
-      <c r="F67" s="15"/>
-      <c r="G67" s="15"/>
-      <c r="H67" s="15"/>
-      <c r="I67" s="15"/>
-      <c r="J67" s="15"/>
-      <c r="K67" s="15"/>
-      <c r="L67" s="15"/>
-      <c r="M67" s="15"/>
-      <c r="N67" s="15"/>
-      <c r="O67" s="15"/>
-      <c r="P67" s="15"/>
-      <c r="Q67" s="15"/>
-      <c r="R67" s="15"/>
-      <c r="S67" s="15"/>
-      <c r="T67" s="15"/>
-      <c r="U67" s="15"/>
+      <c r="A67" s="42" t="s">
+        <v>165</v>
+      </c>
+      <c r="B67" s="42"/>
+      <c r="C67" s="42"/>
+      <c r="D67" s="42"/>
+      <c r="E67" s="42"/>
+      <c r="F67" s="42"/>
+      <c r="G67" s="42"/>
+      <c r="H67" s="42"/>
+      <c r="I67" s="42"/>
+      <c r="J67" s="42"/>
+      <c r="K67" s="42"/>
+      <c r="L67" s="42"/>
+      <c r="M67" s="42"/>
+      <c r="N67" s="42"/>
+      <c r="O67" s="42"/>
+      <c r="P67" s="42"/>
+      <c r="Q67" s="42"/>
+      <c r="R67" s="42"/>
+      <c r="S67" s="42"/>
+      <c r="T67" s="42"/>
+      <c r="U67" s="42"/>
     </row>
     <row r="68" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="44"/>
-      <c r="B68" s="44"/>
+      <c r="A68" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="B68" s="15"/>
       <c r="C68" s="15" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="D68" s="15"/>
-      <c r="E68" s="15"/>
+      <c r="E68" s="15" t="s">
+        <v>168</v>
+      </c>
       <c r="F68" s="15"/>
-      <c r="G68" s="15" t="s">
-        <v>180</v>
-      </c>
+      <c r="G68" s="15"/>
       <c r="H68" s="15"/>
-      <c r="I68" s="15"/>
+      <c r="I68" s="15" t="s">
+        <v>169</v>
+      </c>
       <c r="J68" s="15"/>
       <c r="K68" s="15"/>
       <c r="L68" s="15"/>
       <c r="M68" s="15" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="N68" s="15"/>
       <c r="O68" s="15"/>
       <c r="P68" s="15"/>
       <c r="Q68" s="15"/>
       <c r="R68" s="15" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="S68" s="15"/>
       <c r="T68" s="15"/>
       <c r="U68" s="15"/>
     </row>
-    <row r="69" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="15" t="s">
+    <row r="69" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="43" t="s">
+        <v>172</v>
+      </c>
+      <c r="B69" s="43"/>
+      <c r="C69" s="43" t="s">
+        <v>173</v>
+      </c>
+      <c r="D69" s="43"/>
+      <c r="E69" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="F69" s="43"/>
+      <c r="G69" s="43"/>
+      <c r="H69" s="43"/>
+      <c r="I69" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="J69" s="43"/>
+      <c r="K69" s="43"/>
+      <c r="L69" s="43"/>
+      <c r="M69" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="N69" s="43"/>
+      <c r="O69" s="43"/>
+      <c r="P69" s="43"/>
+      <c r="Q69" s="43"/>
+      <c r="R69" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="S69" s="43"/>
+      <c r="T69" s="43"/>
+      <c r="U69" s="43"/>
+    </row>
+    <row r="70" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="43" t="s">
+        <v>175</v>
+      </c>
+      <c r="B70" s="43"/>
+      <c r="C70" s="43" t="s">
+        <v>176</v>
+      </c>
+      <c r="D70" s="43"/>
+      <c r="E70" s="43" t="s">
+        <v>177</v>
+      </c>
+      <c r="F70" s="43"/>
+      <c r="G70" s="43"/>
+      <c r="H70" s="43"/>
+      <c r="I70" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="J70" s="43"/>
+      <c r="K70" s="43"/>
+      <c r="L70" s="43"/>
+      <c r="M70" s="43" t="s">
+        <v>179</v>
+      </c>
+      <c r="N70" s="43"/>
+      <c r="O70" s="43"/>
+      <c r="P70" s="43"/>
+      <c r="Q70" s="43"/>
+      <c r="R70" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="S70" s="43"/>
+      <c r="T70" s="43"/>
+      <c r="U70" s="43"/>
+    </row>
+    <row r="71" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="B71" s="43"/>
+      <c r="C71" s="43" t="s">
         <v>182</v>
       </c>
-      <c r="B69" s="15"/>
-      <c r="C69" s="20" t="s">
+      <c r="D71" s="43"/>
+      <c r="E71" s="43" t="s">
         <v>183</v>
       </c>
-      <c r="D69" s="20"/>
-      <c r="E69" s="20"/>
-      <c r="F69" s="20"/>
-      <c r="G69" s="20"/>
-      <c r="H69" s="20"/>
-      <c r="I69" s="20"/>
-      <c r="J69" s="20"/>
-      <c r="K69" s="20"/>
-      <c r="L69" s="20"/>
-      <c r="M69" s="20"/>
-      <c r="N69" s="20"/>
-      <c r="O69" s="20"/>
-      <c r="P69" s="20"/>
-      <c r="Q69" s="20"/>
-      <c r="R69" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="S69" s="20"/>
-      <c r="T69" s="20"/>
-      <c r="U69" s="20"/>
-    </row>
-    <row r="70" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="15" t="s">
+      <c r="F71" s="43"/>
+      <c r="G71" s="43"/>
+      <c r="H71" s="43"/>
+      <c r="I71" s="43" t="s">
         <v>184</v>
       </c>
-      <c r="B70" s="15"/>
-      <c r="C70" s="20"/>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="20"/>
-      <c r="H70" s="20"/>
-      <c r="I70" s="20"/>
-      <c r="J70" s="20"/>
-      <c r="K70" s="20"/>
-      <c r="L70" s="20"/>
-      <c r="M70" s="20"/>
-      <c r="N70" s="20"/>
-      <c r="O70" s="20"/>
-      <c r="P70" s="20"/>
-      <c r="Q70" s="20"/>
-      <c r="R70" s="20"/>
-      <c r="S70" s="20"/>
-      <c r="T70" s="20"/>
-      <c r="U70" s="20"/>
-    </row>
-    <row r="71" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="B71" s="15"/>
-      <c r="C71" s="20"/>
-      <c r="D71" s="20"/>
-      <c r="E71" s="20"/>
-      <c r="F71" s="20"/>
-      <c r="G71" s="20"/>
-      <c r="H71" s="20"/>
-      <c r="I71" s="20"/>
-      <c r="J71" s="20"/>
-      <c r="K71" s="20"/>
-      <c r="L71" s="20"/>
-      <c r="M71" s="20"/>
-      <c r="N71" s="20"/>
-      <c r="O71" s="20"/>
-      <c r="P71" s="20"/>
-      <c r="Q71" s="20"/>
-      <c r="R71" s="20"/>
-      <c r="S71" s="20"/>
-      <c r="T71" s="20"/>
-      <c r="U71" s="20"/>
-    </row>
-    <row r="72" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="B72" s="15"/>
-      <c r="C72" s="20"/>
-      <c r="D72" s="20"/>
-      <c r="E72" s="20"/>
-      <c r="F72" s="20"/>
-      <c r="G72" s="20"/>
-      <c r="H72" s="20"/>
-      <c r="I72" s="20"/>
-      <c r="J72" s="20"/>
-      <c r="K72" s="20"/>
-      <c r="L72" s="20"/>
-      <c r="M72" s="20"/>
-      <c r="N72" s="20"/>
-      <c r="O72" s="20"/>
-      <c r="P72" s="20"/>
-      <c r="Q72" s="20"/>
-      <c r="R72" s="20"/>
-      <c r="S72" s="20"/>
-      <c r="T72" s="20"/>
-      <c r="U72" s="20"/>
-    </row>
-    <row r="73" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="15" t="s">
+      <c r="J71" s="43"/>
+      <c r="K71" s="43"/>
+      <c r="L71" s="43"/>
+      <c r="M71" s="43" t="s">
         <v>185</v>
       </c>
-      <c r="B73" s="15"/>
-      <c r="C73" s="20"/>
-      <c r="D73" s="20"/>
-      <c r="E73" s="20"/>
-      <c r="F73" s="20"/>
-      <c r="G73" s="20"/>
-      <c r="H73" s="20"/>
-      <c r="I73" s="20"/>
-      <c r="J73" s="20"/>
-      <c r="K73" s="20"/>
-      <c r="L73" s="20"/>
-      <c r="M73" s="20"/>
-      <c r="N73" s="20"/>
-      <c r="O73" s="20"/>
-      <c r="P73" s="20"/>
-      <c r="Q73" s="20"/>
-      <c r="R73" s="20"/>
-      <c r="S73" s="20"/>
-      <c r="T73" s="20"/>
-      <c r="U73" s="20"/>
+      <c r="N71" s="43"/>
+      <c r="O71" s="43"/>
+      <c r="P71" s="43"/>
+      <c r="Q71" s="43"/>
+      <c r="R71" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="S71" s="43"/>
+      <c r="T71" s="43"/>
+      <c r="U71" s="43"/>
+    </row>
+    <row r="72" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="B72" s="43"/>
+      <c r="C72" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="D72" s="43"/>
+      <c r="E72" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="F72" s="43"/>
+      <c r="G72" s="43"/>
+      <c r="H72" s="43"/>
+      <c r="I72" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="J72" s="43"/>
+      <c r="K72" s="43"/>
+      <c r="L72" s="43"/>
+      <c r="M72" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="N72" s="43"/>
+      <c r="O72" s="43"/>
+      <c r="P72" s="43"/>
+      <c r="Q72" s="43"/>
+      <c r="R72" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="S72" s="43"/>
+      <c r="T72" s="43"/>
+      <c r="U72" s="43"/>
+    </row>
+    <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="74" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="B74" s="15"/>
+      <c r="C74" s="15"/>
+      <c r="D74" s="15"/>
+      <c r="E74" s="15"/>
+      <c r="F74" s="15"/>
+      <c r="G74" s="15"/>
+      <c r="H74" s="15"/>
+      <c r="I74" s="15"/>
+      <c r="J74" s="15"/>
+      <c r="K74" s="15"/>
+      <c r="L74" s="15"/>
+      <c r="M74" s="15"/>
+      <c r="N74" s="15"/>
+      <c r="O74" s="15"/>
+      <c r="P74" s="15"/>
+      <c r="Q74" s="15"/>
+      <c r="R74" s="15"/>
+      <c r="S74" s="15"/>
+      <c r="T74" s="15"/>
+      <c r="U74" s="15"/>
+    </row>
+    <row r="75" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="B75" s="15"/>
+      <c r="C75" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="D75" s="15"/>
+      <c r="E75" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="F75" s="15"/>
+      <c r="G75" s="15"/>
+      <c r="H75" s="15"/>
+      <c r="I75" s="15"/>
+      <c r="J75" s="15"/>
+      <c r="K75" s="15"/>
+      <c r="L75" s="15"/>
+      <c r="M75" s="15"/>
+      <c r="N75" s="15"/>
+      <c r="O75" s="15"/>
+      <c r="P75" s="15"/>
+      <c r="Q75" s="15"/>
+      <c r="R75" s="15"/>
+      <c r="S75" s="15"/>
+      <c r="T75" s="15"/>
+      <c r="U75" s="15"/>
+    </row>
+    <row r="76" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B76" s="20"/>
+      <c r="C76" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="D76" s="20"/>
+      <c r="E76" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="F76" s="22"/>
+      <c r="G76" s="22"/>
+      <c r="H76" s="22"/>
+      <c r="I76" s="22"/>
+      <c r="J76" s="22"/>
+      <c r="K76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="T76" s="22"/>
+      <c r="U76" s="22"/>
+    </row>
+    <row r="77" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="B77" s="20"/>
+      <c r="C77" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="D77" s="20"/>
+      <c r="E77" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="F77" s="22"/>
+      <c r="G77" s="22"/>
+      <c r="H77" s="22"/>
+      <c r="I77" s="22"/>
+      <c r="J77" s="22"/>
+      <c r="K77" s="22"/>
+      <c r="L77" s="22"/>
+      <c r="M77" s="22"/>
+      <c r="N77" s="22"/>
+      <c r="O77" s="22"/>
+      <c r="P77" s="22"/>
+      <c r="Q77" s="22"/>
+      <c r="R77" s="22"/>
+      <c r="S77" s="22"/>
+      <c r="T77" s="22"/>
+      <c r="U77" s="22"/>
+    </row>
+    <row r="78" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="22"/>
+      <c r="B78" s="22"/>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="F78" s="22"/>
+      <c r="G78" s="22"/>
+      <c r="H78" s="22"/>
+      <c r="I78" s="22"/>
+      <c r="J78" s="22"/>
+      <c r="K78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="T78" s="22"/>
+      <c r="U78" s="22"/>
+    </row>
+    <row r="79" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="22"/>
+      <c r="B79" s="22"/>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="22"/>
+      <c r="K79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="T79" s="22"/>
+      <c r="U79" s="22"/>
+    </row>
+    <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="81" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="B81" s="15"/>
+      <c r="C81" s="15"/>
+      <c r="D81" s="15"/>
+      <c r="E81" s="15"/>
+      <c r="F81" s="15"/>
+      <c r="G81" s="15"/>
+      <c r="H81" s="15"/>
+      <c r="I81" s="15"/>
+      <c r="J81" s="15"/>
+      <c r="K81" s="15"/>
+      <c r="L81" s="15"/>
+      <c r="M81" s="15"/>
+      <c r="N81" s="15"/>
+      <c r="O81" s="15"/>
+      <c r="P81" s="15"/>
+      <c r="Q81" s="15"/>
+      <c r="R81" s="15"/>
+      <c r="S81" s="15"/>
+      <c r="T81" s="15"/>
+      <c r="U81" s="15"/>
+    </row>
+    <row r="82" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="44"/>
+      <c r="B82" s="44"/>
+      <c r="C82" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="D82" s="15"/>
+      <c r="E82" s="15"/>
+      <c r="F82" s="15"/>
+      <c r="G82" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="H82" s="15"/>
+      <c r="I82" s="15"/>
+      <c r="J82" s="15"/>
+      <c r="K82" s="15"/>
+      <c r="L82" s="15"/>
+      <c r="M82" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="N82" s="15"/>
+      <c r="O82" s="15"/>
+      <c r="P82" s="15"/>
+      <c r="Q82" s="15"/>
+      <c r="R82" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="S82" s="15"/>
+      <c r="T82" s="15"/>
+      <c r="U82" s="15"/>
+    </row>
+    <row r="83" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="B83" s="15"/>
+      <c r="C83" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="D83" s="20"/>
+      <c r="E83" s="20"/>
+      <c r="F83" s="20"/>
+      <c r="G83" s="20"/>
+      <c r="H83" s="20"/>
+      <c r="I83" s="20"/>
+      <c r="J83" s="20"/>
+      <c r="K83" s="20"/>
+      <c r="L83" s="20"/>
+      <c r="M83" s="20"/>
+      <c r="N83" s="20"/>
+      <c r="O83" s="20"/>
+      <c r="P83" s="20"/>
+      <c r="Q83" s="20"/>
+      <c r="R83" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="S83" s="20"/>
+      <c r="T83" s="20"/>
+      <c r="U83" s="20"/>
+    </row>
+    <row r="84" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="B84" s="15"/>
+      <c r="C84" s="20"/>
+      <c r="D84" s="20"/>
+      <c r="E84" s="20"/>
+      <c r="F84" s="20"/>
+      <c r="G84" s="20"/>
+      <c r="H84" s="20"/>
+      <c r="I84" s="20"/>
+      <c r="J84" s="20"/>
+      <c r="K84" s="20"/>
+      <c r="L84" s="20"/>
+      <c r="M84" s="20"/>
+      <c r="N84" s="20"/>
+      <c r="O84" s="20"/>
+      <c r="P84" s="20"/>
+      <c r="Q84" s="20"/>
+      <c r="R84" s="20"/>
+      <c r="S84" s="20"/>
+      <c r="T84" s="20"/>
+      <c r="U84" s="20"/>
+    </row>
+    <row r="85" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="B85" s="15"/>
+      <c r="C85" s="20"/>
+      <c r="D85" s="20"/>
+      <c r="E85" s="20"/>
+      <c r="F85" s="20"/>
+      <c r="G85" s="20"/>
+      <c r="H85" s="20"/>
+      <c r="I85" s="20"/>
+      <c r="J85" s="20"/>
+      <c r="K85" s="20"/>
+      <c r="L85" s="20"/>
+      <c r="M85" s="20"/>
+      <c r="N85" s="20"/>
+      <c r="O85" s="20"/>
+      <c r="P85" s="20"/>
+      <c r="Q85" s="20"/>
+      <c r="R85" s="20"/>
+      <c r="S85" s="20"/>
+      <c r="T85" s="20"/>
+      <c r="U85" s="20"/>
+    </row>
+    <row r="86" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="B86" s="15"/>
+      <c r="C86" s="20"/>
+      <c r="D86" s="20"/>
+      <c r="E86" s="20"/>
+      <c r="F86" s="20"/>
+      <c r="G86" s="20"/>
+      <c r="H86" s="20"/>
+      <c r="I86" s="20"/>
+      <c r="J86" s="20"/>
+      <c r="K86" s="20"/>
+      <c r="L86" s="20"/>
+      <c r="M86" s="20"/>
+      <c r="N86" s="20"/>
+      <c r="O86" s="20"/>
+      <c r="P86" s="20"/>
+      <c r="Q86" s="20"/>
+      <c r="R86" s="20"/>
+      <c r="S86" s="20"/>
+      <c r="T86" s="20"/>
+      <c r="U86" s="20"/>
+    </row>
+    <row r="87" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="B87" s="15"/>
+      <c r="C87" s="20"/>
+      <c r="D87" s="20"/>
+      <c r="E87" s="20"/>
+      <c r="F87" s="20"/>
+      <c r="G87" s="20"/>
+      <c r="H87" s="20"/>
+      <c r="I87" s="20"/>
+      <c r="J87" s="20"/>
+      <c r="K87" s="20"/>
+      <c r="L87" s="20"/>
+      <c r="M87" s="20"/>
+      <c r="N87" s="20"/>
+      <c r="O87" s="20"/>
+      <c r="P87" s="20"/>
+      <c r="Q87" s="20"/>
+      <c r="R87" s="20"/>
+      <c r="S87" s="20"/>
+      <c r="T87" s="20"/>
+      <c r="U87" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="216">
+  <mergeCells count="251">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="F1:F8"/>
@@ -8735,72 +9583,67 @@
     <mergeCell ref="D11:I11"/>
     <mergeCell ref="J11:O11"/>
     <mergeCell ref="Q11:U11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="J12:O12"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:C13"/>
+    <mergeCell ref="D12:I13"/>
+    <mergeCell ref="J12:O13"/>
+    <mergeCell ref="P12:P13"/>
     <mergeCell ref="Q12:U12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:I13"/>
-    <mergeCell ref="J13:O13"/>
     <mergeCell ref="Q13:U13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:C15"/>
-    <mergeCell ref="D14:I15"/>
-    <mergeCell ref="J14:O15"/>
-    <mergeCell ref="P14:P15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="J14:O14"/>
     <mergeCell ref="Q14:U14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:C16"/>
+    <mergeCell ref="D15:I16"/>
+    <mergeCell ref="J15:O16"/>
+    <mergeCell ref="P15:P16"/>
     <mergeCell ref="Q15:U15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:I16"/>
-    <mergeCell ref="J16:O16"/>
     <mergeCell ref="Q16:U16"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="D17:I17"/>
     <mergeCell ref="J17:O17"/>
     <mergeCell ref="Q17:U17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:C19"/>
-    <mergeCell ref="D18:I19"/>
-    <mergeCell ref="J18:O19"/>
-    <mergeCell ref="P18:P19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="J18:O18"/>
     <mergeCell ref="Q18:U18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:C20"/>
+    <mergeCell ref="D19:I20"/>
+    <mergeCell ref="J19:O20"/>
+    <mergeCell ref="P19:P20"/>
     <mergeCell ref="Q19:U19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:I20"/>
-    <mergeCell ref="J20:O20"/>
     <mergeCell ref="Q20:U20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:C22"/>
-    <mergeCell ref="D21:I22"/>
-    <mergeCell ref="J21:O22"/>
-    <mergeCell ref="P21:P22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:I21"/>
+    <mergeCell ref="J21:O21"/>
     <mergeCell ref="Q21:U21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="D22:I23"/>
+    <mergeCell ref="J22:O23"/>
+    <mergeCell ref="P22:P23"/>
     <mergeCell ref="Q22:U22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:I23"/>
-    <mergeCell ref="J23:O23"/>
     <mergeCell ref="Q23:U23"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="D24:I24"/>
     <mergeCell ref="J24:O24"/>
     <mergeCell ref="Q24:U24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="J25:O25"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:C26"/>
+    <mergeCell ref="D25:I26"/>
+    <mergeCell ref="J25:O26"/>
+    <mergeCell ref="P25:P26"/>
     <mergeCell ref="Q25:U25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:I26"/>
-    <mergeCell ref="J26:O26"/>
     <mergeCell ref="Q26:U26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:I27"/>
-    <mergeCell ref="J27:O27"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="B27:C29"/>
+    <mergeCell ref="D27:I29"/>
+    <mergeCell ref="J27:O29"/>
+    <mergeCell ref="P27:P29"/>
     <mergeCell ref="Q27:U27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:C29"/>
-    <mergeCell ref="D28:I29"/>
-    <mergeCell ref="J28:O29"/>
-    <mergeCell ref="P28:P29"/>
     <mergeCell ref="Q28:U28"/>
     <mergeCell ref="Q29:U29"/>
     <mergeCell ref="B30:C30"/>
@@ -8811,22 +9654,29 @@
     <mergeCell ref="D31:I31"/>
     <mergeCell ref="J31:O31"/>
     <mergeCell ref="Q31:U31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:I32"/>
-    <mergeCell ref="J32:O32"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:C33"/>
+    <mergeCell ref="D32:I33"/>
+    <mergeCell ref="J32:O33"/>
+    <mergeCell ref="P32:P33"/>
     <mergeCell ref="Q32:U32"/>
-    <mergeCell ref="B34:H34"/>
-    <mergeCell ref="I34:U34"/>
-    <mergeCell ref="B35:H35"/>
-    <mergeCell ref="I35:U35"/>
-    <mergeCell ref="B36:H36"/>
-    <mergeCell ref="I36:U36"/>
-    <mergeCell ref="B37:H37"/>
-    <mergeCell ref="I37:U37"/>
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="I38:U38"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="I39:U39"/>
+    <mergeCell ref="Q33:U33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:I34"/>
+    <mergeCell ref="J34:O34"/>
+    <mergeCell ref="Q34:U34"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="B35:C37"/>
+    <mergeCell ref="D35:I37"/>
+    <mergeCell ref="J35:O37"/>
+    <mergeCell ref="P35:P37"/>
+    <mergeCell ref="Q35:U35"/>
+    <mergeCell ref="Q36:U36"/>
+    <mergeCell ref="Q37:U37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:I38"/>
+    <mergeCell ref="J38:O38"/>
+    <mergeCell ref="Q38:U38"/>
     <mergeCell ref="B40:H40"/>
     <mergeCell ref="I40:U40"/>
     <mergeCell ref="B41:H41"/>
@@ -8853,77 +9703,110 @@
     <mergeCell ref="I51:U51"/>
     <mergeCell ref="B52:H52"/>
     <mergeCell ref="I52:U52"/>
-    <mergeCell ref="A55:U55"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="I56:L56"/>
-    <mergeCell ref="M56:Q56"/>
-    <mergeCell ref="R56:U56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="I57:L57"/>
-    <mergeCell ref="M57:Q57"/>
-    <mergeCell ref="R57:U57"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="I58:L58"/>
-    <mergeCell ref="M58:Q58"/>
-    <mergeCell ref="R58:U58"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="I59:L59"/>
-    <mergeCell ref="M59:Q59"/>
-    <mergeCell ref="R59:U59"/>
-    <mergeCell ref="A61:U61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="E62:U62"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="E63:U63"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="E64:U64"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="E65:U65"/>
+    <mergeCell ref="B53:H53"/>
+    <mergeCell ref="I53:U53"/>
+    <mergeCell ref="B54:H54"/>
+    <mergeCell ref="I54:U54"/>
+    <mergeCell ref="B55:H55"/>
+    <mergeCell ref="I55:U55"/>
+    <mergeCell ref="B56:H56"/>
+    <mergeCell ref="I56:U56"/>
+    <mergeCell ref="B57:H57"/>
+    <mergeCell ref="I57:U57"/>
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="I58:U58"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="I59:U59"/>
+    <mergeCell ref="B60:H60"/>
+    <mergeCell ref="I60:U60"/>
+    <mergeCell ref="B61:H61"/>
+    <mergeCell ref="I61:U61"/>
+    <mergeCell ref="B62:H62"/>
+    <mergeCell ref="I62:U62"/>
+    <mergeCell ref="B63:H63"/>
+    <mergeCell ref="I63:U63"/>
+    <mergeCell ref="B64:H64"/>
+    <mergeCell ref="I64:U64"/>
     <mergeCell ref="A67:U67"/>
     <mergeCell ref="A68:B68"/>
-    <mergeCell ref="C68:F68"/>
-    <mergeCell ref="G68:L68"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="I68:L68"/>
     <mergeCell ref="M68:Q68"/>
     <mergeCell ref="R68:U68"/>
     <mergeCell ref="A69:B69"/>
-    <mergeCell ref="C69:F69"/>
-    <mergeCell ref="G69:L69"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="I69:L69"/>
     <mergeCell ref="M69:Q69"/>
     <mergeCell ref="R69:U69"/>
     <mergeCell ref="A70:B70"/>
-    <mergeCell ref="C70:F70"/>
-    <mergeCell ref="G70:L70"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="I70:L70"/>
     <mergeCell ref="M70:Q70"/>
     <mergeCell ref="R70:U70"/>
     <mergeCell ref="A71:B71"/>
-    <mergeCell ref="C71:F71"/>
-    <mergeCell ref="G71:L71"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="I71:L71"/>
     <mergeCell ref="M71:Q71"/>
     <mergeCell ref="R71:U71"/>
     <mergeCell ref="A72:B72"/>
-    <mergeCell ref="C72:F72"/>
-    <mergeCell ref="G72:L72"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="I72:L72"/>
     <mergeCell ref="M72:Q72"/>
     <mergeCell ref="R72:U72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:F73"/>
-    <mergeCell ref="G73:L73"/>
-    <mergeCell ref="M73:Q73"/>
-    <mergeCell ref="R73:U73"/>
+    <mergeCell ref="A74:U74"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="E75:U75"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="E76:U76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="E77:U77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="E78:U78"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="E79:U79"/>
+    <mergeCell ref="A81:U81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="C82:F82"/>
+    <mergeCell ref="G82:L82"/>
+    <mergeCell ref="M82:Q82"/>
+    <mergeCell ref="R82:U82"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="C83:F83"/>
+    <mergeCell ref="G83:L83"/>
+    <mergeCell ref="M83:Q83"/>
+    <mergeCell ref="R83:U83"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="C84:F84"/>
+    <mergeCell ref="G84:L84"/>
+    <mergeCell ref="M84:Q84"/>
+    <mergeCell ref="R84:U84"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="C85:F85"/>
+    <mergeCell ref="G85:L85"/>
+    <mergeCell ref="M85:Q85"/>
+    <mergeCell ref="R85:U85"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="C86:F86"/>
+    <mergeCell ref="G86:L86"/>
+    <mergeCell ref="M86:Q86"/>
+    <mergeCell ref="R86:U86"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="C87:F87"/>
+    <mergeCell ref="G87:L87"/>
+    <mergeCell ref="M87:Q87"/>
+    <mergeCell ref="R87:U87"/>
   </mergeCells>
-  <conditionalFormatting sqref="P12:P32">
+  <conditionalFormatting sqref="P12:P38">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("N",P12)))</formula>
     </cfRule>
@@ -8946,7 +9829,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="S4:S6 P12:P32" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="S4:S6 P12:P38" type="list">
       <formula1>"N,$,L"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -8958,10 +9841,12 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <rowBreaks count="3" manualBreakCount="3">
+  <rowBreaks count="5" manualBreakCount="5">
     <brk id="16" man="true" max="16383" min="0"/>
-    <brk id="22" man="true" max="16383" min="0"/>
-    <brk id="27" man="true" max="16383" min="0"/>
+    <brk id="21" man="true" max="16383" min="0"/>
+    <brk id="26" man="true" max="16383" min="0"/>
+    <brk id="31" man="true" max="16383" min="0"/>
+    <brk id="37" man="true" max="16383" min="0"/>
   </rowBreaks>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -8989,7 +9874,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="45" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -9014,18 +9899,18 @@
     </row>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="47" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="B2" s="47"/>
       <c r="C2" s="22" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
       <c r="H2" s="47" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="I2" s="47"/>
       <c r="J2" s="47"/>
@@ -9042,7 +9927,7 @@
     </row>
     <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="47" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="B3" s="47"/>
       <c r="C3" s="22" t="s">
@@ -9053,13 +9938,13 @@
       <c r="F3" s="22"/>
       <c r="G3" s="22"/>
       <c r="H3" s="47" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="I3" s="47"/>
       <c r="J3" s="47"/>
       <c r="K3" s="47"/>
       <c r="L3" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="22"/>
       <c r="N3" s="22"/>
@@ -9070,11 +9955,11 @@
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="47" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="B4" s="47"/>
       <c r="C4" s="22" t="s">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="D4" s="22"/>
       <c r="E4" s="22"/>
@@ -9098,12 +9983,12 @@
         <v>40</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="C6" s="48"/>
       <c r="D6" s="48"/>
       <c r="E6" s="48" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="F6" s="48"/>
       <c r="G6" s="48"/>
@@ -9112,18 +9997,18 @@
       <c r="J6" s="48"/>
       <c r="K6" s="48"/>
       <c r="L6" s="15" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="M6" s="15"/>
       <c r="N6" s="15"/>
       <c r="O6" s="48" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="P6" s="48"/>
       <c r="Q6" s="48"/>
       <c r="R6" s="48"/>
       <c r="S6" s="15" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="T6" s="15"/>
       <c r="U6" s="15"/>
@@ -9141,39 +10026,39 @@
       <c r="J7" s="48"/>
       <c r="K7" s="48"/>
       <c r="L7" s="49" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="M7" s="49" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="N7" s="49" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="O7" s="48"/>
       <c r="P7" s="48"/>
       <c r="Q7" s="48"/>
       <c r="R7" s="48"/>
       <c r="S7" s="49" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="T7" s="49" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="U7" s="49" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="50" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="C8" s="22"/>
       <c r="D8" s="22"/>
       <c r="E8" s="22" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="F8" s="22"/>
       <c r="G8" s="22"/>
@@ -9192,7 +10077,7 @@
         <v>M</v>
       </c>
       <c r="O8" s="22" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="P8" s="22"/>
       <c r="Q8" s="22"/>
@@ -9210,15 +10095,15 @@
     </row>
     <row r="9" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="50" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="C9" s="22"/>
       <c r="D9" s="22"/>
       <c r="E9" s="22" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="F9" s="22"/>
       <c r="G9" s="22"/>
@@ -9237,7 +10122,7 @@
         <v>T</v>
       </c>
       <c r="O9" s="22" t="s">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="P9" s="22"/>
       <c r="Q9" s="22"/>
@@ -9255,15 +10140,15 @@
     </row>
     <row r="10" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="50" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="C10" s="22"/>
       <c r="D10" s="22"/>
       <c r="E10" s="22" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="F10" s="22"/>
       <c r="G10" s="22"/>
@@ -9282,7 +10167,7 @@
         <v>M</v>
       </c>
       <c r="O10" s="22" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="P10" s="22"/>
       <c r="Q10" s="22"/>
@@ -9303,12 +10188,12 @@
         <v>99</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="C11" s="22"/>
       <c r="D11" s="22"/>
       <c r="E11" s="22" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="F11" s="22"/>
       <c r="G11" s="22"/>
@@ -9327,7 +10212,7 @@
         <v>T</v>
       </c>
       <c r="O11" s="22" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="P11" s="22"/>
       <c r="Q11" s="22"/>
@@ -9348,12 +10233,12 @@
         <v>99</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="C12" s="22"/>
       <c r="D12" s="22"/>
       <c r="E12" s="22" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="F12" s="22"/>
       <c r="G12" s="22"/>
@@ -9372,7 +10257,7 @@
         <v>T</v>
       </c>
       <c r="O12" s="22" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="P12" s="22"/>
       <c r="Q12" s="22"/>
@@ -9390,15 +10275,15 @@
     </row>
     <row r="13" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="50" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="C13" s="22"/>
       <c r="D13" s="22"/>
       <c r="E13" s="22" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="F13" s="22"/>
       <c r="G13" s="22"/>
@@ -9417,7 +10302,7 @@
         <v>M</v>
       </c>
       <c r="O13" s="22" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="P13" s="22"/>
       <c r="Q13" s="22"/>
@@ -9435,15 +10320,15 @@
     </row>
     <row r="14" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="50" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="C14" s="22"/>
       <c r="D14" s="22"/>
       <c r="E14" s="22" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="F14" s="22"/>
       <c r="G14" s="22"/>
@@ -9462,7 +10347,7 @@
         <v>M</v>
       </c>
       <c r="O14" s="22" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="P14" s="22"/>
       <c r="Q14" s="22"/>
@@ -9480,11 +10365,11 @@
     </row>
     <row r="16" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="52" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="B16" s="52"/>
       <c r="C16" s="53" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="D16" s="53"/>
       <c r="E16" s="53"/>
@@ -9507,7 +10392,7 @@
     </row>
     <row r="18" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="54" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="B18" s="54"/>
       <c r="C18" s="54"/>
@@ -9538,7 +10423,7 @@
       <c r="E19" s="55"/>
       <c r="F19" s="55"/>
       <c r="G19" s="54" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="H19" s="54"/>
       <c r="I19" s="54"/>
@@ -9557,7 +10442,7 @@
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="56" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="B20" s="56"/>
       <c r="C20" s="56"/>
@@ -9598,40 +10483,40 @@
       <c r="E21" s="56"/>
       <c r="F21" s="56"/>
       <c r="G21" s="57" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="H21" s="57"/>
       <c r="I21" s="57"/>
       <c r="J21" s="57" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="K21" s="57"/>
       <c r="L21" s="57"/>
       <c r="M21" s="57" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="N21" s="57"/>
       <c r="O21" s="57"/>
       <c r="P21" s="57" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="Q21" s="57"/>
       <c r="R21" s="57"/>
       <c r="S21" s="57" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="T21" s="57"/>
       <c r="U21" s="57"/>
     </row>
     <row r="22" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="58" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="B22" s="56" t="n">
         <v>5</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="D22" s="59"/>
       <c r="E22" s="59"/>
@@ -9668,7 +10553,7 @@
         <v>4</v>
       </c>
       <c r="C23" s="59" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="D23" s="59"/>
       <c r="E23" s="59"/>
@@ -9705,7 +10590,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="59" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="D24" s="59"/>
       <c r="E24" s="59"/>
@@ -9742,7 +10627,7 @@
         <v>2</v>
       </c>
       <c r="C25" s="59" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="D25" s="59"/>
       <c r="E25" s="59"/>
@@ -9779,7 +10664,7 @@
         <v>1</v>
       </c>
       <c r="C26" s="59" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="D26" s="59"/>
       <c r="E26" s="59"/>
@@ -9812,22 +10697,22 @@
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="64" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="57" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="B29" s="57"/>
       <c r="C29" s="57"/>
       <c r="D29" s="57" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="E29" s="57"/>
       <c r="F29" s="57"/>
       <c r="G29" s="57" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="H29" s="57"/>
       <c r="I29" s="57"/>
@@ -9846,7 +10731,7 @@
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="65" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="B30" s="65"/>
       <c r="C30" s="65"/>
@@ -9856,7 +10741,7 @@
       <c r="E30" s="66"/>
       <c r="F30" s="66"/>
       <c r="G30" s="22" t="s">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="H30" s="22"/>
       <c r="I30" s="22"/>
@@ -9875,17 +10760,17 @@
     </row>
     <row r="31" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="67" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="B31" s="67"/>
       <c r="C31" s="67"/>
       <c r="D31" s="66" t="s">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="E31" s="66"/>
       <c r="F31" s="66"/>
       <c r="G31" s="22" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="H31" s="22"/>
       <c r="I31" s="22"/>
@@ -9904,17 +10789,17 @@
     </row>
     <row r="32" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="68" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="B32" s="68"/>
       <c r="C32" s="68"/>
       <c r="D32" s="66" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="E32" s="66"/>
       <c r="F32" s="66"/>
       <c r="G32" s="22" t="s">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="H32" s="22"/>
       <c r="I32" s="22"/>
@@ -9933,17 +10818,17 @@
     </row>
     <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="69" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="B33" s="69"/>
       <c r="C33" s="69"/>
       <c r="D33" s="66" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="E33" s="66"/>
       <c r="F33" s="66"/>
       <c r="G33" s="22" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="H33" s="22"/>
       <c r="I33" s="22"/>
@@ -9962,17 +10847,17 @@
     </row>
     <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="70" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="B34" s="70"/>
       <c r="C34" s="70"/>
       <c r="D34" s="66" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="E34" s="66"/>
       <c r="F34" s="66"/>
       <c r="G34" s="22" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="H34" s="22"/>
       <c r="I34" s="22"/>
@@ -10151,7 +11036,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -10164,7 +11049,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="71" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="B1" s="71"/>
       <c r="C1" s="71"/>
@@ -10174,7 +11059,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
@@ -10184,22 +11069,22 @@
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10207,16 +11092,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="72" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="C4" s="73" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="F4" s="21" t="s">
         <v>99</v>
@@ -10227,16 +11112,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="75" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="C5" s="76" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="D5" s="77" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="E5" s="77" t="s">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="F5" s="74" t="s">
         <v>99</v>
@@ -10247,16 +11132,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="72" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="C6" s="73" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="F6" s="21" t="s">
         <v>99</v>
@@ -10267,19 +11152,19 @@
         <v>4</v>
       </c>
       <c r="B7" s="75" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="C7" s="76" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="D7" s="77" t="s">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="E7" s="77" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="F7" s="74" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10287,39 +11172,39 @@
         <v>5</v>
       </c>
       <c r="B8" s="72" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="C8" s="73" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="74" t="n">
         <v>6</v>
       </c>
       <c r="B9" s="75" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="C9" s="76" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="D9" s="77" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="E9" s="77" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F9" s="74" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10327,19 +11212,19 @@
         <v>7</v>
       </c>
       <c r="B10" s="72" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="C10" s="73" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10347,79 +11232,79 @@
         <v>8</v>
       </c>
       <c r="B11" s="75" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C11" s="76" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="D11" s="77" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="E11" s="77" t="s">
-        <v>296</v>
+        <v>316</v>
       </c>
       <c r="F11" s="74" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="n">
         <v>9</v>
       </c>
       <c r="B12" s="72" t="s">
-        <v>293</v>
+        <v>317</v>
       </c>
       <c r="C12" s="73" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="74" t="n">
         <v>10</v>
       </c>
       <c r="B13" s="75" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="C13" s="76" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
       <c r="D13" s="77" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="E13" s="77" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="F13" s="74" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="n">
         <v>11</v>
       </c>
       <c r="B14" s="72" t="s">
-        <v>300</v>
+        <v>324</v>
       </c>
       <c r="C14" s="73" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10427,59 +11312,59 @@
         <v>12</v>
       </c>
       <c r="B15" s="75" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="C15" s="76" t="s">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="D15" s="77" t="s">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="E15" s="77" t="s">
-        <v>306</v>
+        <v>330</v>
       </c>
       <c r="F15" s="74" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="n">
         <v>13</v>
       </c>
       <c r="B16" s="72" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="C16" s="73" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>313</v>
+        <v>333</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>118</v>
+        <v>334</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="74" t="n">
         <v>14</v>
       </c>
       <c r="B17" s="75" t="s">
-        <v>289</v>
+        <v>331</v>
       </c>
       <c r="C17" s="76" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="D17" s="77" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="E17" s="77" t="s">
-        <v>121</v>
+        <v>337</v>
       </c>
       <c r="F17" s="74" t="s">
-        <v>316</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10487,19 +11372,19 @@
         <v>15</v>
       </c>
       <c r="B18" s="72" t="s">
-        <v>289</v>
+        <v>338</v>
       </c>
       <c r="C18" s="73" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10507,19 +11392,19 @@
         <v>16</v>
       </c>
       <c r="B19" s="75" t="s">
-        <v>289</v>
+        <v>342</v>
       </c>
       <c r="C19" s="76" t="s">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="D19" s="77" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="E19" s="77" t="s">
-        <v>323</v>
+        <v>124</v>
       </c>
       <c r="F19" s="74" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10527,19 +11412,19 @@
         <v>17</v>
       </c>
       <c r="B20" s="72" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="C20" s="73" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>326</v>
+        <v>127</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>119</v>
+        <v>347</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10547,19 +11432,19 @@
         <v>18</v>
       </c>
       <c r="B21" s="75" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="C21" s="76" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="D21" s="77" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="E21" s="77" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="F21" s="74" t="s">
-        <v>320</v>
+        <v>351</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10567,19 +11452,19 @@
         <v>19</v>
       </c>
       <c r="B22" s="72" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="C22" s="73" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>320</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10587,39 +11472,39 @@
         <v>20</v>
       </c>
       <c r="B23" s="75" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="C23" s="76" t="s">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="D23" s="77" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="E23" s="77" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="F23" s="74" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="n">
         <v>21</v>
       </c>
       <c r="B24" s="72" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="C24" s="73" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>119</v>
+        <v>351</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10627,19 +11512,19 @@
         <v>22</v>
       </c>
       <c r="B25" s="75" t="s">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="C25" s="76" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="D25" s="77" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="E25" s="77" t="s">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="F25" s="74" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10647,39 +11532,39 @@
         <v>23</v>
       </c>
       <c r="B26" s="72" t="s">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="C26" s="73" t="s">
-        <v>345</v>
+        <v>364</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>347</v>
+        <v>366</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="74" t="n">
         <v>24</v>
       </c>
       <c r="B27" s="75" t="s">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="C27" s="76" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="D27" s="77" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="E27" s="77" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="F27" s="74" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10687,19 +11572,19 @@
         <v>25</v>
       </c>
       <c r="B28" s="72" t="s">
-        <v>340</v>
+        <v>371</v>
       </c>
       <c r="C28" s="73" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="F28" s="21" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10707,19 +11592,19 @@
         <v>26</v>
       </c>
       <c r="B29" s="75" t="s">
-        <v>340</v>
+        <v>371</v>
       </c>
       <c r="C29" s="76" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="D29" s="77" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="E29" s="77" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="F29" s="74" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10727,19 +11612,19 @@
         <v>27</v>
       </c>
       <c r="B30" s="72" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="C30" s="73" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="F30" s="21" t="s">
-        <v>362</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10747,19 +11632,19 @@
         <v>28</v>
       </c>
       <c r="B31" s="75" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="C31" s="76" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="D31" s="77" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="E31" s="77" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="F31" s="74" t="s">
-        <v>127</v>
+        <v>385</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10767,39 +11652,39 @@
         <v>29</v>
       </c>
       <c r="B32" s="72" t="s">
-        <v>307</v>
+        <v>371</v>
       </c>
       <c r="C32" s="73" t="s">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="D32" s="22" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="E32" s="22" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="74" t="n">
         <v>30</v>
       </c>
       <c r="B33" s="75" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="C33" s="76" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="D33" s="77" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="E33" s="77" t="s">
-        <v>373</v>
+        <v>392</v>
       </c>
       <c r="F33" s="74" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10807,59 +11692,59 @@
         <v>31</v>
       </c>
       <c r="B34" s="72" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="C34" s="73" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
       <c r="E34" s="22" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="F34" s="21" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="74" t="n">
         <v>32</v>
       </c>
       <c r="B35" s="75" t="s">
-        <v>370</v>
+        <v>338</v>
       </c>
       <c r="C35" s="76" t="s">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="D35" s="77" t="s">
-        <v>379</v>
+        <v>398</v>
       </c>
       <c r="E35" s="77" t="s">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="F35" s="74" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="n">
         <v>33</v>
       </c>
       <c r="B36" s="72" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="C36" s="73" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="D36" s="22" t="s">
-        <v>383</v>
+        <v>403</v>
       </c>
       <c r="E36" s="22" t="s">
-        <v>384</v>
+        <v>404</v>
       </c>
       <c r="F36" s="21" t="s">
-        <v>385</v>
+        <v>405</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10867,39 +11752,39 @@
         <v>34</v>
       </c>
       <c r="B37" s="75" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="C37" s="76" t="s">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="D37" s="77" t="s">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="E37" s="77" t="s">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="F37" s="74" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="21" t="n">
         <v>35</v>
       </c>
       <c r="B38" s="72" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="C38" s="73" t="s">
+        <v>409</v>
+      </c>
+      <c r="D38" s="22" t="s">
+        <v>410</v>
+      </c>
+      <c r="E38" s="22" t="s">
+        <v>411</v>
+      </c>
+      <c r="F38" s="21" t="s">
         <v>139</v>
-      </c>
-      <c r="D38" s="22" t="s">
-        <v>390</v>
-      </c>
-      <c r="E38" s="22" t="s">
-        <v>391</v>
-      </c>
-      <c r="F38" s="21" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10907,19 +11792,19 @@
         <v>36</v>
       </c>
       <c r="B39" s="75" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="C39" s="76" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="D39" s="77" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E39" s="77" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="F39" s="74" t="s">
-        <v>130</v>
+        <v>416</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10927,39 +11812,39 @@
         <v>37</v>
       </c>
       <c r="B40" s="72" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="C40" s="73" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="D40" s="22" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="E40" s="22" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="F40" s="21" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="74" t="n">
         <v>38</v>
       </c>
       <c r="B41" s="75" t="s">
-        <v>401</v>
+        <v>420</v>
       </c>
       <c r="C41" s="76" t="s">
-        <v>402</v>
+        <v>145</v>
       </c>
       <c r="D41" s="77" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="E41" s="77" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="F41" s="74" t="s">
-        <v>144</v>
+        <v>416</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10967,19 +11852,19 @@
         <v>39</v>
       </c>
       <c r="B42" s="72" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="C42" s="73" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
       <c r="D42" s="22" t="s">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="E42" s="22" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="F42" s="21" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10987,19 +11872,19 @@
         <v>40</v>
       </c>
       <c r="B43" s="75" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="C43" s="76" t="s">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="D43" s="77" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="E43" s="77" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="F43" s="74" t="s">
-        <v>147</v>
+        <v>431</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11007,23 +11892,163 @@
         <v>41</v>
       </c>
       <c r="B44" s="72" t="s">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="C44" s="73" t="s">
-        <v>414</v>
+        <v>433</v>
       </c>
       <c r="D44" s="22" t="s">
-        <v>415</v>
+        <v>434</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>416</v>
+        <v>435</v>
       </c>
       <c r="F44" s="21" t="s">
-        <v>417</v>
+        <v>158</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="74" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="75" t="s">
+        <v>436</v>
+      </c>
+      <c r="C45" s="76" t="s">
+        <v>437</v>
+      </c>
+      <c r="D45" s="77" t="s">
+        <v>438</v>
+      </c>
+      <c r="E45" s="77" t="s">
+        <v>439</v>
+      </c>
+      <c r="F45" s="74" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="21" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="72" t="s">
+        <v>440</v>
+      </c>
+      <c r="C46" s="73" t="s">
+        <v>441</v>
+      </c>
+      <c r="D46" s="22" t="s">
+        <v>442</v>
+      </c>
+      <c r="E46" s="22" t="s">
+        <v>443</v>
+      </c>
+      <c r="F46" s="21" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="74" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="75" t="s">
+        <v>444</v>
+      </c>
+      <c r="C47" s="76" t="s">
+        <v>445</v>
+      </c>
+      <c r="D47" s="77" t="s">
+        <v>446</v>
+      </c>
+      <c r="E47" s="77" t="s">
+        <v>447</v>
+      </c>
+      <c r="F47" s="74" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="72" t="s">
+        <v>444</v>
+      </c>
+      <c r="C48" s="73" t="s">
+        <v>448</v>
+      </c>
+      <c r="D48" s="22" t="s">
+        <v>449</v>
+      </c>
+      <c r="E48" s="22" t="s">
+        <v>450</v>
+      </c>
+      <c r="F48" s="21" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="74" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="75" t="s">
+        <v>451</v>
+      </c>
+      <c r="C49" s="76" t="s">
+        <v>452</v>
+      </c>
+      <c r="D49" s="77" t="s">
+        <v>453</v>
+      </c>
+      <c r="E49" s="77" t="s">
+        <v>454</v>
+      </c>
+      <c r="F49" s="74" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="21" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="72" t="s">
+        <v>456</v>
+      </c>
+      <c r="C50" s="73" t="s">
+        <v>457</v>
+      </c>
+      <c r="D50" s="22" t="s">
+        <v>458</v>
+      </c>
+      <c r="E50" s="22" t="s">
+        <v>459</v>
+      </c>
+      <c r="F50" s="21" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="74" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="75" t="s">
+        <v>460</v>
+      </c>
+      <c r="C51" s="76" t="s">
+        <v>461</v>
+      </c>
+      <c r="D51" s="77" t="s">
+        <v>462</v>
+      </c>
+      <c r="E51" s="77" t="s">
+        <v>463</v>
+      </c>
+      <c r="F51" s="74" t="s">
+        <v>155</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F44"/>
+  <autoFilter ref="A3:F51"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -11044,7 +12069,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -11055,7 +12080,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="71" t="s">
-        <v>418</v>
+        <v>464</v>
       </c>
       <c r="B1" s="71"/>
       <c r="C1" s="71"/>
@@ -11063,7 +12088,7 @@
     </row>
     <row r="3" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="78" t="s">
-        <v>419</v>
+        <v>465</v>
       </c>
       <c r="B3" s="78"/>
       <c r="C3" s="78"/>
@@ -11071,7 +12096,7 @@
     </row>
     <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="22" t="s">
-        <v>420</v>
+        <v>466</v>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
@@ -11079,7 +12104,7 @@
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="78" t="s">
-        <v>421</v>
+        <v>467</v>
       </c>
       <c r="B6" s="78"/>
       <c r="C6" s="78"/>
@@ -11087,7 +12112,7 @@
     </row>
     <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="s">
-        <v>422</v>
+        <v>468</v>
       </c>
       <c r="B7" s="22"/>
       <c r="C7" s="22"/>
@@ -11095,7 +12120,7 @@
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="78" t="s">
-        <v>423</v>
+        <v>469</v>
       </c>
       <c r="B9" s="78"/>
       <c r="C9" s="78"/>
@@ -11103,47 +12128,47 @@
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="72" t="s">
-        <v>424</v>
+        <v>470</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>425</v>
+        <v>471</v>
       </c>
       <c r="C10" s="22"/>
       <c r="D10" s="22"/>
     </row>
     <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="72" t="s">
-        <v>426</v>
+        <v>472</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>427</v>
+        <v>473</v>
       </c>
       <c r="C11" s="22"/>
       <c r="D11" s="22"/>
     </row>
     <row r="12" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="72" t="s">
-        <v>428</v>
+        <v>474</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>429</v>
+        <v>475</v>
       </c>
       <c r="C12" s="22"/>
       <c r="D12" s="22"/>
     </row>
     <row r="13" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="72" t="s">
-        <v>430</v>
+        <v>476</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>431</v>
+        <v>477</v>
       </c>
       <c r="C13" s="22"/>
       <c r="D13" s="22"/>
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="78" t="s">
-        <v>432</v>
+        <v>478</v>
       </c>
       <c r="B15" s="78"/>
       <c r="C15" s="78"/>
@@ -11151,7 +12176,7 @@
     </row>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="22" t="s">
-        <v>433</v>
+        <v>479</v>
       </c>
       <c r="B16" s="22"/>
       <c r="C16" s="22"/>
@@ -11159,7 +12184,7 @@
     </row>
     <row r="17" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="22" t="s">
-        <v>434</v>
+        <v>480</v>
       </c>
       <c r="B17" s="22"/>
       <c r="C17" s="22"/>
@@ -11167,7 +12192,7 @@
     </row>
     <row r="18" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="22" t="s">
-        <v>435</v>
+        <v>481</v>
       </c>
       <c r="B18" s="22"/>
       <c r="C18" s="22"/>
@@ -11175,7 +12200,7 @@
     </row>
     <row r="19" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="22" t="s">
-        <v>436</v>
+        <v>482</v>
       </c>
       <c r="B19" s="22"/>
       <c r="C19" s="22"/>
@@ -11183,7 +12208,7 @@
     </row>
     <row r="20" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="22" t="s">
-        <v>437</v>
+        <v>483</v>
       </c>
       <c r="B20" s="22"/>
       <c r="C20" s="22"/>
@@ -11191,7 +12216,7 @@
     </row>
     <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="78" t="s">
-        <v>438</v>
+        <v>484</v>
       </c>
       <c r="B22" s="78"/>
       <c r="C22" s="78"/>
@@ -11199,103 +12224,103 @@
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="79" t="s">
-        <v>439</v>
+        <v>485</v>
       </c>
       <c r="B23" s="79" t="s">
-        <v>440</v>
+        <v>486</v>
       </c>
       <c r="C23" s="79" t="s">
-        <v>441</v>
+        <v>487</v>
       </c>
       <c r="D23" s="79"/>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="72" t="s">
-        <v>442</v>
+        <v>488</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>443</v>
+        <v>489</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>444</v>
+        <v>490</v>
       </c>
       <c r="D24" s="22"/>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="72" t="s">
-        <v>445</v>
+        <v>491</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>446</v>
+        <v>492</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>447</v>
+        <v>493</v>
       </c>
       <c r="D25" s="22"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="72" t="s">
-        <v>448</v>
+        <v>494</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>443</v>
+        <v>489</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>449</v>
+        <v>495</v>
       </c>
       <c r="D26" s="22"/>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="72" t="s">
-        <v>450</v>
+        <v>496</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>451</v>
+        <v>497</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>452</v>
+        <v>498</v>
       </c>
       <c r="D27" s="22"/>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="72" t="s">
-        <v>453</v>
+        <v>499</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>454</v>
+        <v>500</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>455</v>
+        <v>501</v>
       </c>
       <c r="D28" s="22"/>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="72" t="s">
-        <v>456</v>
+        <v>502</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>457</v>
+        <v>503</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>458</v>
+        <v>504</v>
       </c>
       <c r="D29" s="22"/>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="72" t="s">
-        <v>459</v>
+        <v>505</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>460</v>
+        <v>506</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>461</v>
+        <v>507</v>
       </c>
       <c r="D30" s="22"/>
     </row>
     <row r="31" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="22" t="s">
-        <v>462</v>
+        <v>508</v>
       </c>
       <c r="B31" s="22"/>
       <c r="C31" s="22"/>
@@ -11303,7 +12328,7 @@
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="78" t="s">
-        <v>463</v>
+        <v>509</v>
       </c>
       <c r="B33" s="78"/>
       <c r="C33" s="78"/>
@@ -11311,133 +12336,133 @@
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="79" t="s">
-        <v>464</v>
+        <v>510</v>
       </c>
       <c r="B34" s="79" t="s">
-        <v>465</v>
+        <v>511</v>
       </c>
       <c r="C34" s="79" t="s">
-        <v>466</v>
+        <v>512</v>
       </c>
       <c r="D34" s="79" t="s">
-        <v>467</v>
+        <v>513</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="72" t="s">
-        <v>468</v>
+        <v>514</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>469</v>
+        <v>515</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>468</v>
+        <v>514</v>
       </c>
       <c r="D35" s="22" t="s">
-        <v>470</v>
+        <v>516</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="72" t="s">
-        <v>471</v>
+        <v>517</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>472</v>
+        <v>518</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>471</v>
+        <v>517</v>
       </c>
       <c r="D36" s="22" t="s">
-        <v>473</v>
+        <v>519</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="72" t="s">
-        <v>474</v>
+        <v>520</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>475</v>
+        <v>521</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>474</v>
+        <v>520</v>
       </c>
       <c r="D37" s="22" t="s">
-        <v>476</v>
+        <v>522</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="72" t="s">
-        <v>307</v>
+        <v>338</v>
       </c>
       <c r="B38" s="22" t="s">
-        <v>477</v>
+        <v>523</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>478</v>
+        <v>524</v>
       </c>
       <c r="D38" s="22" t="s">
-        <v>307</v>
+        <v>338</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="72" t="s">
-        <v>479</v>
+        <v>525</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>469</v>
+        <v>515</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>480</v>
+        <v>526</v>
       </c>
       <c r="D39" s="22" t="s">
-        <v>481</v>
+        <v>527</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="72" t="s">
-        <v>482</v>
+        <v>528</v>
       </c>
       <c r="B40" s="22" t="s">
-        <v>483</v>
+        <v>529</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>484</v>
+        <v>530</v>
       </c>
       <c r="D40" s="22" t="s">
-        <v>485</v>
+        <v>531</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="72" t="s">
-        <v>486</v>
+        <v>532</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>487</v>
+        <v>533</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>488</v>
+        <v>534</v>
       </c>
       <c r="D41" s="22" t="s">
-        <v>489</v>
+        <v>535</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="72" t="s">
-        <v>490</v>
+        <v>536</v>
       </c>
       <c r="B42" s="22" t="s">
-        <v>491</v>
+        <v>537</v>
       </c>
       <c r="C42" s="22" t="s">
-        <v>492</v>
+        <v>538</v>
       </c>
       <c r="D42" s="22" t="s">
-        <v>493</v>
+        <v>539</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="78" t="s">
-        <v>494</v>
+        <v>540</v>
       </c>
       <c r="B44" s="78"/>
       <c r="C44" s="78"/>
@@ -11445,199 +12470,239 @@
     </row>
     <row r="45" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="72" t="s">
-        <v>495</v>
+        <v>541</v>
       </c>
       <c r="B45" s="22" t="s">
-        <v>496</v>
+        <v>542</v>
       </c>
       <c r="C45" s="22"/>
       <c r="D45" s="22"/>
     </row>
     <row r="46" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="72" t="s">
-        <v>497</v>
+        <v>543</v>
       </c>
       <c r="B46" s="22" t="s">
-        <v>498</v>
+        <v>544</v>
       </c>
       <c r="C46" s="22"/>
       <c r="D46" s="22"/>
     </row>
     <row r="47" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="72" t="s">
-        <v>499</v>
+        <v>545</v>
       </c>
       <c r="B47" s="22" t="s">
-        <v>500</v>
+        <v>546</v>
       </c>
       <c r="C47" s="22"/>
       <c r="D47" s="22"/>
     </row>
     <row r="48" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="72" t="s">
-        <v>501</v>
+        <v>547</v>
       </c>
       <c r="B48" s="22" t="s">
-        <v>502</v>
+        <v>548</v>
       </c>
       <c r="C48" s="22"/>
       <c r="D48" s="22"/>
     </row>
     <row r="49" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="72" t="s">
-        <v>503</v>
+        <v>549</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>504</v>
+        <v>550</v>
       </c>
       <c r="C49" s="22"/>
       <c r="D49" s="22"/>
     </row>
     <row r="50" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="72" t="s">
-        <v>505</v>
+        <v>551</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>506</v>
+        <v>552</v>
       </c>
       <c r="C50" s="22"/>
       <c r="D50" s="22"/>
     </row>
     <row r="51" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="72" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
       <c r="B51" s="22" t="s">
-        <v>508</v>
+        <v>554</v>
       </c>
       <c r="C51" s="22"/>
       <c r="D51" s="22"/>
     </row>
-    <row r="53" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="78" t="s">
-        <v>509</v>
-      </c>
-      <c r="B53" s="78"/>
-      <c r="C53" s="78"/>
-      <c r="D53" s="78"/>
+    <row r="52" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="72" t="s">
+        <v>555</v>
+      </c>
+      <c r="B52" s="22" t="s">
+        <v>556</v>
+      </c>
+      <c r="C52" s="22"/>
+      <c r="D52" s="22"/>
+    </row>
+    <row r="53" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="72" t="s">
+        <v>557</v>
+      </c>
+      <c r="B53" s="22" t="s">
+        <v>558</v>
+      </c>
+      <c r="C53" s="22"/>
+      <c r="D53" s="22"/>
     </row>
     <row r="54" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="72" t="s">
-        <v>510</v>
+        <v>559</v>
       </c>
       <c r="B54" s="22" t="s">
-        <v>511</v>
+        <v>560</v>
       </c>
       <c r="C54" s="22"/>
       <c r="D54" s="22"/>
     </row>
-    <row r="55" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="72" t="s">
-        <v>512</v>
-      </c>
-      <c r="B55" s="22" t="s">
-        <v>513</v>
-      </c>
-      <c r="C55" s="22"/>
-      <c r="D55" s="22"/>
-    </row>
-    <row r="56" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="72" t="s">
-        <v>514</v>
-      </c>
-      <c r="B56" s="22" t="s">
-        <v>515</v>
-      </c>
-      <c r="C56" s="22"/>
-      <c r="D56" s="22"/>
+    <row r="56" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="78" t="s">
+        <v>561</v>
+      </c>
+      <c r="B56" s="78"/>
+      <c r="C56" s="78"/>
+      <c r="D56" s="78"/>
     </row>
     <row r="57" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="72" t="s">
-        <v>516</v>
+        <v>562</v>
       </c>
       <c r="B57" s="22" t="s">
-        <v>517</v>
+        <v>563</v>
       </c>
       <c r="C57" s="22"/>
       <c r="D57" s="22"/>
     </row>
     <row r="58" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="72" t="s">
-        <v>518</v>
+        <v>564</v>
       </c>
       <c r="B58" s="22" t="s">
-        <v>519</v>
+        <v>565</v>
       </c>
       <c r="C58" s="22"/>
       <c r="D58" s="22"/>
     </row>
     <row r="59" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="72" t="s">
-        <v>520</v>
+        <v>566</v>
       </c>
       <c r="B59" s="22" t="s">
-        <v>521</v>
+        <v>567</v>
       </c>
       <c r="C59" s="22"/>
       <c r="D59" s="22"/>
     </row>
     <row r="60" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="72" t="s">
-        <v>522</v>
+        <v>568</v>
       </c>
       <c r="B60" s="22" t="s">
-        <v>523</v>
+        <v>569</v>
       </c>
       <c r="C60" s="22"/>
       <c r="D60" s="22"/>
     </row>
-    <row r="62" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="78" t="s">
-        <v>524</v>
-      </c>
-      <c r="B62" s="78"/>
-      <c r="C62" s="78"/>
-      <c r="D62" s="78"/>
+    <row r="61" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="72" t="s">
+        <v>570</v>
+      </c>
+      <c r="B61" s="22" t="s">
+        <v>571</v>
+      </c>
+      <c r="C61" s="22"/>
+      <c r="D61" s="22"/>
+    </row>
+    <row r="62" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="72" t="s">
+        <v>572</v>
+      </c>
+      <c r="B62" s="22" t="s">
+        <v>573</v>
+      </c>
+      <c r="C62" s="22"/>
+      <c r="D62" s="22"/>
     </row>
     <row r="63" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="22" t="s">
-        <v>525</v>
-      </c>
-      <c r="B63" s="22"/>
+      <c r="A63" s="72" t="s">
+        <v>574</v>
+      </c>
+      <c r="B63" s="22" t="s">
+        <v>575</v>
+      </c>
       <c r="C63" s="22"/>
       <c r="D63" s="22"/>
     </row>
     <row r="64" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="22" t="s">
-        <v>526</v>
-      </c>
-      <c r="B64" s="22"/>
+      <c r="A64" s="72" t="s">
+        <v>576</v>
+      </c>
+      <c r="B64" s="22" t="s">
+        <v>577</v>
+      </c>
       <c r="C64" s="22"/>
       <c r="D64" s="22"/>
     </row>
-    <row r="65" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="22" t="s">
-        <v>527</v>
-      </c>
-      <c r="B65" s="22"/>
-      <c r="C65" s="22"/>
-      <c r="D65" s="22"/>
-    </row>
-    <row r="66" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="22" t="s">
-        <v>528</v>
-      </c>
-      <c r="B66" s="22"/>
-      <c r="C66" s="22"/>
-      <c r="D66" s="22"/>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="80" t="s">
-        <v>529</v>
+    <row r="66" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="78" t="s">
+        <v>578</v>
+      </c>
+      <c r="B66" s="78"/>
+      <c r="C66" s="78"/>
+      <c r="D66" s="78"/>
+    </row>
+    <row r="67" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="22" t="s">
+        <v>579</v>
+      </c>
+      <c r="B67" s="22"/>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+    </row>
+    <row r="68" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="22" t="s">
+        <v>580</v>
+      </c>
+      <c r="B68" s="22"/>
+      <c r="C68" s="22"/>
+      <c r="D68" s="22"/>
+    </row>
+    <row r="69" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="22" t="s">
+        <v>581</v>
+      </c>
+      <c r="B69" s="22"/>
+      <c r="C69" s="22"/>
+      <c r="D69" s="22"/>
+    </row>
+    <row r="70" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="22" t="s">
+        <v>582</v>
+      </c>
+      <c r="B70" s="22"/>
+      <c r="C70" s="22"/>
+      <c r="D70" s="22"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="80" t="s">
+        <v>583</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="48">
+  <mergeCells count="52">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A4:D4"/>
@@ -11673,19 +12738,23 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="B51:D51"/>
-    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B53:D53"/>
     <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="A56:D56"/>
     <mergeCell ref="B57:D57"/>
     <mergeCell ref="B58:D58"/>
     <mergeCell ref="B59:D59"/>
     <mergeCell ref="B60:D60"/>
-    <mergeCell ref="A62:D62"/>
-    <mergeCell ref="A63:D63"/>
-    <mergeCell ref="A64:D64"/>
-    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B64:D64"/>
     <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A70:D70"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
